--- a/research/traditional_assets/database/data/brazil/brazil_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_hotel_gaming.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.013</v>
+        <v>-0.0373</v>
       </c>
       <c r="G2">
-        <v>-0.2862238074008025</v>
+        <v>0.02394143252869015</v>
       </c>
       <c r="H2">
-        <v>-0.2862238074008025</v>
+        <v>0.02394143252869015</v>
       </c>
       <c r="I2">
-        <v>-0.1337494427106554</v>
+        <v>-0.074000791452315</v>
       </c>
       <c r="J2">
-        <v>-0.1337494427106554</v>
+        <v>-0.074000791452315</v>
       </c>
       <c r="K2">
-        <v>-89.40000000000001</v>
+        <v>-95.90000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.398573339277753</v>
+        <v>-0.3795013850415513</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>74.3</v>
+        <v>44.4</v>
       </c>
       <c r="V2">
-        <v>0.3129738837405223</v>
+        <v>0.1382746807848022</v>
       </c>
       <c r="W2">
-        <v>-0.9322210636079249</v>
+        <v>-1.021299254526091</v>
       </c>
       <c r="X2">
-        <v>0.1653716551018649</v>
+        <v>0.1289615489965141</v>
       </c>
       <c r="Y2">
-        <v>-1.09759271870979</v>
+        <v>-1.150260803522606</v>
       </c>
       <c r="Z2">
-        <v>1.912190963341858</v>
+        <v>2.163527397260274</v>
       </c>
       <c r="AA2">
-        <v>-0.2557544757033248</v>
+        <v>-0.1601027397260274</v>
       </c>
       <c r="AB2">
-        <v>0.1191507478016404</v>
+        <v>0.1045216984112477</v>
       </c>
       <c r="AC2">
-        <v>-0.3749052235049652</v>
+        <v>-0.2646244381372751</v>
       </c>
       <c r="AD2">
-        <v>187.4</v>
+        <v>165</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>187.4</v>
+        <v>165</v>
       </c>
       <c r="AG2">
-        <v>113.1</v>
+        <v>120.6</v>
       </c>
       <c r="AH2">
-        <v>0.4411487758945386</v>
+        <v>0.3394363299732565</v>
       </c>
       <c r="AI2">
-        <v>0.7090427544457056</v>
+        <v>0.6537242472266244</v>
       </c>
       <c r="AJ2">
-        <v>0.3226818830242511</v>
+        <v>0.2730359972832239</v>
       </c>
       <c r="AK2">
-        <v>0.5952631578947369</v>
+        <v>0.5798076923076922</v>
       </c>
       <c r="AL2">
-        <v>49.4</v>
+        <v>65.7</v>
       </c>
       <c r="AM2">
-        <v>35.8</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="AN2">
-        <v>-12.01282051282051</v>
+        <v>-6.179775280898877</v>
       </c>
       <c r="AO2">
-        <v>-0.6072874493927126</v>
+        <v>-0.2846270928462709</v>
       </c>
       <c r="AP2">
-        <v>-7.250000000000001</v>
+        <v>-4.51685393258427</v>
       </c>
       <c r="AQ2">
-        <v>-0.8379888268156426</v>
+        <v>-0.3437499999999999</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.013</v>
+        <v>-0.0373</v>
       </c>
       <c r="G3">
-        <v>-0.2862238074008025</v>
+        <v>0.02394143252869015</v>
       </c>
       <c r="H3">
-        <v>-0.2862238074008025</v>
+        <v>0.02394143252869015</v>
       </c>
       <c r="I3">
-        <v>-0.1337494427106554</v>
+        <v>-0.074000791452315</v>
       </c>
       <c r="J3">
-        <v>-0.1337494427106554</v>
+        <v>-0.074000791452315</v>
       </c>
       <c r="K3">
-        <v>-89.40000000000001</v>
+        <v>-95.90000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.398573339277753</v>
+        <v>-0.3795013850415513</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>74.3</v>
+        <v>44.4</v>
       </c>
       <c r="V3">
-        <v>0.3129738837405223</v>
+        <v>0.1382746807848022</v>
       </c>
       <c r="W3">
-        <v>-0.9322210636079249</v>
+        <v>-1.021299254526091</v>
       </c>
       <c r="X3">
-        <v>0.1653716551018649</v>
+        <v>0.1289615489965141</v>
       </c>
       <c r="Y3">
-        <v>-1.09759271870979</v>
+        <v>-1.150260803522606</v>
       </c>
       <c r="Z3">
-        <v>1.912190963341858</v>
+        <v>2.163527397260274</v>
       </c>
       <c r="AA3">
-        <v>-0.2557544757033248</v>
+        <v>-0.1601027397260274</v>
       </c>
       <c r="AB3">
-        <v>0.1191507478016404</v>
+        <v>0.1045216984112477</v>
       </c>
       <c r="AC3">
-        <v>-0.3749052235049652</v>
+        <v>-0.2646244381372751</v>
       </c>
       <c r="AD3">
-        <v>187.4</v>
+        <v>165</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>187.4</v>
+        <v>165</v>
       </c>
       <c r="AG3">
-        <v>113.1</v>
+        <v>120.6</v>
       </c>
       <c r="AH3">
-        <v>0.4411487758945386</v>
+        <v>0.3394363299732565</v>
       </c>
       <c r="AI3">
-        <v>0.7090427544457056</v>
+        <v>0.6537242472266244</v>
       </c>
       <c r="AJ3">
-        <v>0.3226818830242511</v>
+        <v>0.2730359972832239</v>
       </c>
       <c r="AK3">
-        <v>0.5952631578947369</v>
+        <v>0.5798076923076922</v>
       </c>
       <c r="AL3">
-        <v>49.4</v>
+        <v>65.7</v>
       </c>
       <c r="AM3">
-        <v>35.8</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="AN3">
-        <v>-12.01282051282051</v>
+        <v>-6.179775280898877</v>
       </c>
       <c r="AO3">
-        <v>-0.6072874493927126</v>
+        <v>-0.2846270928462709</v>
       </c>
       <c r="AP3">
-        <v>-7.250000000000001</v>
+        <v>-4.51685393258427</v>
       </c>
       <c r="AQ3">
-        <v>-0.8379888268156426</v>
+        <v>-0.3437499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/brazil/brazil_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_hotel_gaming.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1031948963688802</v>
+        <v>0.102873733721226</v>
       </c>
       <c r="C2">
-        <v>268.577408481511</v>
+        <v>266.2358561678532</v>
       </c>
       <c r="D2">
-        <v>198.1774084815111</v>
+        <v>198.6088561678532</v>
       </c>
       <c r="E2">
-        <v>-160</v>
+        <v>-157.227</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.773</v>
       </c>
       <c r="G2">
         <v>70.40000000000001</v>
@@ -1439,28 +1439,28 @@
         <v>12</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1394819</v>
       </c>
       <c r="N2">
-        <v>12</v>
+        <v>11.8605181</v>
       </c>
       <c r="O2">
-        <v>4.08</v>
+        <v>4.032576154</v>
       </c>
       <c r="P2">
-        <v>7.92</v>
+        <v>7.827941946</v>
       </c>
       <c r="Q2">
-        <v>49.32</v>
+        <v>49.227941946</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1031948963688802</v>
+        <v>0.1035775290113394</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7530348907127269</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>86.03266803793181</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.102873733721226</v>
+        <v>0.1025525710735718</v>
       </c>
       <c r="C3">
-        <v>266.2358561678532</v>
+        <v>263.8961865435337</v>
       </c>
       <c r="D3">
-        <v>198.6088561678532</v>
+        <v>199.0421865435337</v>
       </c>
       <c r="E3">
-        <v>-157.227</v>
+        <v>-154.454</v>
       </c>
       <c r="F3">
-        <v>2.773</v>
+        <v>5.546</v>
       </c>
       <c r="G3">
         <v>70.40000000000001</v>
@@ -1521,28 +1521,28 @@
         <v>12</v>
       </c>
       <c r="M3">
-        <v>0.1394819</v>
+        <v>0.2789638</v>
       </c>
       <c r="N3">
-        <v>11.8605181</v>
+        <v>11.7210362</v>
       </c>
       <c r="O3">
-        <v>4.032576154</v>
+        <v>3.985152308</v>
       </c>
       <c r="P3">
-        <v>7.827941946</v>
+        <v>7.735883892</v>
       </c>
       <c r="Q3">
-        <v>49.227941946</v>
+        <v>49.135883892</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1035775290113394</v>
+        <v>0.1039679704832365</v>
       </c>
       <c r="T3">
-        <v>0.7530348907127269</v>
+        <v>0.7581236519690637</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>86.03266803793181</v>
+        <v>43.01633401896591</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1025525710735718</v>
+        <v>0.1022314084259176</v>
       </c>
       <c r="C4">
-        <v>263.8961865435337</v>
+        <v>261.5584119586115</v>
       </c>
       <c r="D4">
-        <v>199.0421865435337</v>
+        <v>199.4774119586116</v>
       </c>
       <c r="E4">
-        <v>-154.454</v>
+        <v>-151.681</v>
       </c>
       <c r="F4">
-        <v>5.546</v>
+        <v>8.319000000000001</v>
       </c>
       <c r="G4">
         <v>70.40000000000001</v>
@@ -1603,28 +1603,28 @@
         <v>12</v>
       </c>
       <c r="M4">
-        <v>0.2789638</v>
+        <v>0.4184457</v>
       </c>
       <c r="N4">
-        <v>11.7210362</v>
+        <v>11.5815543</v>
       </c>
       <c r="O4">
-        <v>3.985152308</v>
+        <v>3.937728462</v>
       </c>
       <c r="P4">
-        <v>7.735883892</v>
+        <v>7.643825838</v>
       </c>
       <c r="Q4">
-        <v>49.135883892</v>
+        <v>49.043825838</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1039679704832365</v>
+        <v>0.1043664622947604</v>
       </c>
       <c r="T4">
-        <v>0.7581236519690637</v>
+        <v>0.7633173361379025</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>43.01633401896591</v>
+        <v>28.67755601264393</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1022314084259176</v>
+        <v>0.1019102457782634</v>
       </c>
       <c r="C5">
-        <v>261.5584119586115</v>
+        <v>259.2225448714012</v>
       </c>
       <c r="D5">
-        <v>199.4774119586116</v>
+        <v>199.9145448714011</v>
       </c>
       <c r="E5">
-        <v>-151.681</v>
+        <v>-148.908</v>
       </c>
       <c r="F5">
-        <v>8.319000000000001</v>
+        <v>11.092</v>
       </c>
       <c r="G5">
         <v>70.40000000000001</v>
@@ -1685,28 +1685,28 @@
         <v>12</v>
       </c>
       <c r="M5">
-        <v>0.4184457</v>
+        <v>0.5579276</v>
       </c>
       <c r="N5">
-        <v>11.5815543</v>
+        <v>11.4420724</v>
       </c>
       <c r="O5">
-        <v>3.937728462</v>
+        <v>3.890304616</v>
       </c>
       <c r="P5">
-        <v>7.643825838</v>
+        <v>7.551767784000001</v>
       </c>
       <c r="Q5">
-        <v>49.043825838</v>
+        <v>48.951767784</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1043664622947604</v>
+        <v>0.1047732560190244</v>
       </c>
       <c r="T5">
-        <v>0.7633173361379025</v>
+        <v>0.7686192220602586</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.67755601264393</v>
+        <v>21.50816700948295</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1019102457782634</v>
+        <v>0.1015890831306092</v>
       </c>
       <c r="C6">
-        <v>259.2225448714012</v>
+        <v>256.8885978496604</v>
       </c>
       <c r="D6">
-        <v>199.9145448714011</v>
+        <v>200.3535978496604</v>
       </c>
       <c r="E6">
-        <v>-148.908</v>
+        <v>-146.135</v>
       </c>
       <c r="F6">
-        <v>11.092</v>
+        <v>13.865</v>
       </c>
       <c r="G6">
         <v>70.40000000000001</v>
@@ -1767,28 +1767,28 @@
         <v>12</v>
       </c>
       <c r="M6">
-        <v>0.5579276</v>
+        <v>0.6974095</v>
       </c>
       <c r="N6">
-        <v>11.4420724</v>
+        <v>11.3025905</v>
       </c>
       <c r="O6">
-        <v>3.890304616</v>
+        <v>3.842880770000001</v>
       </c>
       <c r="P6">
-        <v>7.551767784000001</v>
+        <v>7.45970973</v>
       </c>
       <c r="Q6">
-        <v>48.951767784</v>
+        <v>48.85970973</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1047732560190244</v>
+        <v>0.1051886138216939</v>
       </c>
       <c r="T6">
-        <v>0.7686192220602586</v>
+        <v>0.7740327266336117</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.50816700948295</v>
+        <v>17.20653360758636</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1015890831306092</v>
+        <v>0.101267920482955</v>
       </c>
       <c r="C7">
-        <v>256.8885978496604</v>
+        <v>254.556583571796</v>
       </c>
       <c r="D7">
-        <v>200.3535978496604</v>
+        <v>200.794583571796</v>
       </c>
       <c r="E7">
-        <v>-146.135</v>
+        <v>-143.362</v>
       </c>
       <c r="F7">
-        <v>13.865</v>
+        <v>16.638</v>
       </c>
       <c r="G7">
         <v>70.40000000000001</v>
@@ -1849,28 +1849,28 @@
         <v>12</v>
       </c>
       <c r="M7">
-        <v>0.6974095</v>
+        <v>0.8368914000000001</v>
       </c>
       <c r="N7">
-        <v>11.3025905</v>
+        <v>11.1631086</v>
       </c>
       <c r="O7">
-        <v>3.842880770000001</v>
+        <v>3.795456924</v>
       </c>
       <c r="P7">
-        <v>7.45970973</v>
+        <v>7.367651675999999</v>
       </c>
       <c r="Q7">
-        <v>48.85970973</v>
+        <v>48.767651676</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1051886138216939</v>
+        <v>0.1056128090244202</v>
       </c>
       <c r="T7">
-        <v>0.7740327266336117</v>
+        <v>0.779561412155334</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.20653360758636</v>
+        <v>14.33877800632196</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.101267920482955</v>
+        <v>0.1010160578353008</v>
       </c>
       <c r="C8">
-        <v>254.556583571796</v>
+        <v>252.1307745208224</v>
       </c>
       <c r="D8">
-        <v>200.794583571796</v>
+        <v>201.1417745208224</v>
       </c>
       <c r="E8">
-        <v>-143.362</v>
+        <v>-140.589</v>
       </c>
       <c r="F8">
-        <v>16.638</v>
+        <v>19.411</v>
       </c>
       <c r="G8">
         <v>70.40000000000001</v>
@@ -1931,45 +1931,45 @@
         <v>12</v>
       </c>
       <c r="M8">
-        <v>0.8368914000000001</v>
+        <v>1.0054898</v>
       </c>
       <c r="N8">
-        <v>11.1631086</v>
+        <v>10.9945102</v>
       </c>
       <c r="O8">
-        <v>3.795456924</v>
+        <v>3.738133468</v>
       </c>
       <c r="P8">
-        <v>7.367651675999999</v>
+        <v>7.256376732</v>
       </c>
       <c r="Q8">
-        <v>48.767651676</v>
+        <v>48.656376732</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1056128090244202</v>
+        <v>0.1060461267046245</v>
       </c>
       <c r="T8">
-        <v>0.779561412155334</v>
+        <v>0.7852089941398889</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.34</v>
       </c>
       <c r="W8">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.33877800632196</v>
+        <v>11.9344820802757</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1010160578353008</v>
+        <v>0.1007047951876466</v>
       </c>
       <c r="C9">
-        <v>252.1307745208224</v>
+        <v>249.7885103005694</v>
       </c>
       <c r="D9">
-        <v>201.1417745208224</v>
+        <v>201.5725103005694</v>
       </c>
       <c r="E9">
-        <v>-140.589</v>
+        <v>-137.816</v>
       </c>
       <c r="F9">
-        <v>19.411</v>
+        <v>22.184</v>
       </c>
       <c r="G9">
         <v>70.40000000000001</v>
@@ -2013,28 +2013,28 @@
         <v>12</v>
       </c>
       <c r="M9">
-        <v>1.0054898</v>
+        <v>1.1491312</v>
       </c>
       <c r="N9">
-        <v>10.9945102</v>
+        <v>10.8508688</v>
       </c>
       <c r="O9">
-        <v>3.738133468</v>
+        <v>3.689295392</v>
       </c>
       <c r="P9">
-        <v>7.256376732</v>
+        <v>7.161573408000001</v>
       </c>
       <c r="Q9">
-        <v>48.656376732</v>
+        <v>48.561573408</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1060461267046246</v>
+        <v>0.1064888643343985</v>
       </c>
       <c r="T9">
-        <v>0.7852089941398891</v>
+        <v>0.7909793496458473</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.9344820802757</v>
+        <v>10.44267182024124</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1007047951876466</v>
+        <v>0.1004945125399924</v>
       </c>
       <c r="C10">
-        <v>249.7885103005694</v>
+        <v>247.3075521992461</v>
       </c>
       <c r="D10">
-        <v>201.5725103005694</v>
+        <v>201.8645521992461</v>
       </c>
       <c r="E10">
-        <v>-137.816</v>
+        <v>-135.043</v>
       </c>
       <c r="F10">
-        <v>22.184</v>
+        <v>24.957</v>
       </c>
       <c r="G10">
         <v>70.40000000000001</v>
@@ -2095,45 +2095,45 @@
         <v>12</v>
       </c>
       <c r="M10">
-        <v>1.1491312</v>
+        <v>1.3351995</v>
       </c>
       <c r="N10">
-        <v>10.8508688</v>
+        <v>10.6648005</v>
       </c>
       <c r="O10">
-        <v>3.689295392</v>
+        <v>3.62603217</v>
       </c>
       <c r="P10">
-        <v>7.161573408000001</v>
+        <v>7.03876833</v>
       </c>
       <c r="Q10">
-        <v>48.561573408</v>
+        <v>48.43876833</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1064888643343985</v>
+        <v>0.1069413324615302</v>
       </c>
       <c r="T10">
-        <v>0.7909793496458473</v>
+        <v>0.7968765261519367</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.34</v>
       </c>
       <c r="W10">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.44267182024124</v>
+        <v>8.987420980909594</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1004945125399924</v>
+        <v>0.1001944698923383</v>
       </c>
       <c r="C11">
-        <v>247.3075521992461</v>
+        <v>244.9527215510226</v>
       </c>
       <c r="D11">
-        <v>201.8645521992461</v>
+        <v>202.2827215510226</v>
       </c>
       <c r="E11">
-        <v>-135.043</v>
+        <v>-132.27</v>
       </c>
       <c r="F11">
-        <v>24.957</v>
+        <v>27.73</v>
       </c>
       <c r="G11">
         <v>70.40000000000001</v>
@@ -2177,28 +2177,28 @@
         <v>12</v>
       </c>
       <c r="M11">
-        <v>1.3351995</v>
+        <v>1.483555</v>
       </c>
       <c r="N11">
-        <v>10.6648005</v>
+        <v>10.516445</v>
       </c>
       <c r="O11">
-        <v>3.62603217</v>
+        <v>3.575591300000001</v>
       </c>
       <c r="P11">
-        <v>7.03876833</v>
+        <v>6.9408537</v>
       </c>
       <c r="Q11">
-        <v>48.43876833</v>
+        <v>48.3408537</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1069413324615302</v>
+        <v>0.1074038554359314</v>
       </c>
       <c r="T11">
-        <v>0.7968765261519367</v>
+        <v>0.8029047510248281</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.987420980909594</v>
+        <v>8.088678882818636</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1001944698923383</v>
+        <v>0.09995250724468406</v>
       </c>
       <c r="C12">
-        <v>244.9527215510226</v>
+        <v>242.5182088504358</v>
       </c>
       <c r="D12">
-        <v>202.2827215510226</v>
+        <v>202.6212088504357</v>
       </c>
       <c r="E12">
-        <v>-132.27</v>
+        <v>-129.497</v>
       </c>
       <c r="F12">
-        <v>27.73</v>
+        <v>30.503</v>
       </c>
       <c r="G12">
         <v>70.40000000000001</v>
@@ -2259,45 +2259,45 @@
         <v>12</v>
       </c>
       <c r="M12">
-        <v>1.483555</v>
+        <v>1.6563129</v>
       </c>
       <c r="N12">
-        <v>10.516445</v>
+        <v>10.3436871</v>
       </c>
       <c r="O12">
-        <v>3.5755913</v>
+        <v>3.516853614</v>
       </c>
       <c r="P12">
-        <v>6.940853699999999</v>
+        <v>6.826833486</v>
       </c>
       <c r="Q12">
-        <v>48.3408537</v>
+        <v>48.226833486</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1074038554359314</v>
+        <v>0.1078767721850383</v>
       </c>
       <c r="T12">
-        <v>0.8029047510248281</v>
+        <v>0.8090684416252001</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.34</v>
       </c>
       <c r="W12">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.088678882818634</v>
+        <v>7.24500787260668</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09995250724468406</v>
+        <v>0.09965774459702986</v>
       </c>
       <c r="C13">
-        <v>242.5182088504358</v>
+        <v>240.1590930235732</v>
       </c>
       <c r="D13">
-        <v>202.6212088504357</v>
+        <v>203.0350930235732</v>
       </c>
       <c r="E13">
-        <v>-129.497</v>
+        <v>-126.724</v>
       </c>
       <c r="F13">
-        <v>30.503</v>
+        <v>33.276</v>
       </c>
       <c r="G13">
         <v>70.40000000000001</v>
@@ -2341,28 +2341,28 @@
         <v>12</v>
       </c>
       <c r="M13">
-        <v>1.6563129</v>
+        <v>1.8068868</v>
       </c>
       <c r="N13">
-        <v>10.3436871</v>
+        <v>10.1931132</v>
       </c>
       <c r="O13">
-        <v>3.516853614</v>
+        <v>3.465658488</v>
       </c>
       <c r="P13">
-        <v>6.826833486</v>
+        <v>6.727454711999999</v>
       </c>
       <c r="Q13">
-        <v>48.226833486</v>
+        <v>48.127454712</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1078767721850383</v>
+        <v>0.1083604370420794</v>
       </c>
       <c r="T13">
-        <v>0.8090684416252001</v>
+        <v>0.8153722161028534</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.24500787260668</v>
+        <v>6.641257216556122</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09965774459702986</v>
+        <v>0.09936298194937568</v>
       </c>
       <c r="C14">
-        <v>240.1590930235732</v>
+        <v>237.8016714984284</v>
       </c>
       <c r="D14">
-        <v>203.0350930235732</v>
+        <v>203.4506714984284</v>
       </c>
       <c r="E14">
-        <v>-126.724</v>
+        <v>-123.951</v>
       </c>
       <c r="F14">
-        <v>33.276</v>
+        <v>36.049</v>
       </c>
       <c r="G14">
         <v>70.40000000000001</v>
@@ -2423,28 +2423,28 @@
         <v>12</v>
       </c>
       <c r="M14">
-        <v>1.8068868</v>
+        <v>1.9574607</v>
       </c>
       <c r="N14">
-        <v>10.1931132</v>
+        <v>10.0425393</v>
       </c>
       <c r="O14">
-        <v>3.465658488</v>
+        <v>3.414463362</v>
       </c>
       <c r="P14">
-        <v>6.727454711999999</v>
+        <v>6.628075937999999</v>
       </c>
       <c r="Q14">
-        <v>48.127454712</v>
+        <v>48.028075938</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1083604370420794</v>
+        <v>0.1088552206314663</v>
       </c>
       <c r="T14">
-        <v>0.8153722161028534</v>
+        <v>0.8218209049363148</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.641257216556122</v>
+        <v>6.130391276821037</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09936298194937568</v>
+        <v>0.09916061930172149</v>
       </c>
       <c r="C15">
-        <v>237.8016714984284</v>
+        <v>235.3149638000344</v>
       </c>
       <c r="D15">
-        <v>203.4506714984284</v>
+        <v>203.7369638000344</v>
       </c>
       <c r="E15">
-        <v>-123.951</v>
+        <v>-121.178</v>
       </c>
       <c r="F15">
-        <v>36.049</v>
+        <v>38.822</v>
       </c>
       <c r="G15">
         <v>70.40000000000001</v>
@@ -2505,45 +2505,45 @@
         <v>12</v>
       </c>
       <c r="M15">
-        <v>1.9574607</v>
+        <v>2.1468566</v>
       </c>
       <c r="N15">
-        <v>10.0425393</v>
+        <v>9.8531434</v>
       </c>
       <c r="O15">
-        <v>3.414463362</v>
+        <v>3.350068756</v>
       </c>
       <c r="P15">
-        <v>6.628075937999999</v>
+        <v>6.503074644</v>
       </c>
       <c r="Q15">
-        <v>48.028075938</v>
+        <v>47.903074644</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1088552206314663</v>
+        <v>0.1093615108159552</v>
       </c>
       <c r="T15">
-        <v>0.8218209049363148</v>
+        <v>0.8284195632775309</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.34</v>
       </c>
       <c r="W15">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.130391276821037</v>
+        <v>5.589567556584822</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09916061930172149</v>
+        <v>0.09887245665406728</v>
       </c>
       <c r="C16">
-        <v>235.3149638000344</v>
+        <v>232.9510349243494</v>
       </c>
       <c r="D16">
-        <v>203.7369638000344</v>
+        <v>204.1460349243495</v>
       </c>
       <c r="E16">
-        <v>-121.178</v>
+        <v>-118.405</v>
       </c>
       <c r="F16">
-        <v>38.822</v>
+        <v>41.59500000000001</v>
       </c>
       <c r="G16">
         <v>70.40000000000001</v>
@@ -2587,28 +2587,28 @@
         <v>12</v>
       </c>
       <c r="M16">
-        <v>2.1468566</v>
+        <v>2.3002035</v>
       </c>
       <c r="N16">
-        <v>9.8531434</v>
+        <v>9.6997965</v>
       </c>
       <c r="O16">
-        <v>3.350068756</v>
+        <v>3.29793081</v>
       </c>
       <c r="P16">
-        <v>6.503074644</v>
+        <v>6.401865689999999</v>
       </c>
       <c r="Q16">
-        <v>47.903074644</v>
+        <v>47.80186569</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1093615108159552</v>
+        <v>0.1098797137106674</v>
       </c>
       <c r="T16">
-        <v>0.8284195632775309</v>
+        <v>0.8351734841679523</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.589567556584822</v>
+        <v>5.216929719479167</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09887245665406728</v>
+        <v>0.09858429400641308</v>
       </c>
       <c r="C17">
-        <v>232.9510349243494</v>
+        <v>230.5887520519014</v>
       </c>
       <c r="D17">
-        <v>204.1460349243495</v>
+        <v>204.5567520519014</v>
       </c>
       <c r="E17">
-        <v>-118.405</v>
+        <v>-115.632</v>
       </c>
       <c r="F17">
-        <v>41.595</v>
+        <v>44.368</v>
       </c>
       <c r="G17">
         <v>70.40000000000001</v>
@@ -2669,28 +2669,28 @@
         <v>12</v>
       </c>
       <c r="M17">
-        <v>2.3002035</v>
+        <v>2.4535504</v>
       </c>
       <c r="N17">
-        <v>9.6997965</v>
+        <v>9.546449599999999</v>
       </c>
       <c r="O17">
-        <v>3.29793081</v>
+        <v>3.245792864</v>
       </c>
       <c r="P17">
-        <v>6.401865689999999</v>
+        <v>6.300656735999999</v>
       </c>
       <c r="Q17">
-        <v>47.80186569</v>
+        <v>47.700656736</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1098797137106674</v>
+        <v>0.1104102547695394</v>
       </c>
       <c r="T17">
-        <v>0.8351734841679523</v>
+        <v>0.8420882126986218</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.216929719479168</v>
+        <v>4.890871612011719</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09858429400641308</v>
+        <v>0.09829613135875891</v>
       </c>
       <c r="C18">
-        <v>230.5887520519014</v>
+        <v>228.228125137396</v>
       </c>
       <c r="D18">
-        <v>204.5567520519014</v>
+        <v>204.969125137396</v>
       </c>
       <c r="E18">
-        <v>-115.632</v>
+        <v>-112.859</v>
       </c>
       <c r="F18">
-        <v>44.368</v>
+        <v>47.14100000000001</v>
       </c>
       <c r="G18">
         <v>70.40000000000001</v>
@@ -2751,28 +2751,28 @@
         <v>12</v>
       </c>
       <c r="M18">
-        <v>2.4535504</v>
+        <v>2.6068973</v>
       </c>
       <c r="N18">
-        <v>9.546449599999999</v>
+        <v>9.3931027</v>
       </c>
       <c r="O18">
-        <v>3.245792864</v>
+        <v>3.193654918</v>
       </c>
       <c r="P18">
-        <v>6.300656735999999</v>
+        <v>6.199447782</v>
       </c>
       <c r="Q18">
-        <v>47.700656736</v>
+        <v>47.599447782</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1104102547695394</v>
+        <v>0.1109535799503119</v>
       </c>
       <c r="T18">
-        <v>0.8420882126986218</v>
+        <v>0.8491695611938858</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.890871612011719</v>
+        <v>4.603173281893383</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09829613135875891</v>
+        <v>0.09830496871110472</v>
       </c>
       <c r="C19">
-        <v>228.228125137396</v>
+        <v>225.4424537964668</v>
       </c>
       <c r="D19">
-        <v>204.969125137396</v>
+        <v>204.9564537964668</v>
       </c>
       <c r="E19">
-        <v>-112.859</v>
+        <v>-110.086</v>
       </c>
       <c r="F19">
-        <v>47.14100000000001</v>
+        <v>49.91400000000001</v>
       </c>
       <c r="G19">
         <v>70.40000000000001</v>
@@ -2833,45 +2833,45 @@
         <v>12</v>
       </c>
       <c r="M19">
-        <v>2.6068973</v>
+        <v>2.885029200000001</v>
       </c>
       <c r="N19">
-        <v>9.3931027</v>
+        <v>9.114970799999998</v>
       </c>
       <c r="O19">
-        <v>3.193654918</v>
+        <v>3.099090072</v>
       </c>
       <c r="P19">
-        <v>6.199447782</v>
+        <v>6.015880727999999</v>
       </c>
       <c r="Q19">
-        <v>47.599447782</v>
+        <v>47.415880728</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1109535799503119</v>
+        <v>0.1115101569647619</v>
       </c>
       <c r="T19">
-        <v>0.8491695611938858</v>
+        <v>0.8564236255061073</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.34</v>
       </c>
       <c r="W19">
-        <v>0.036498</v>
+        <v>0.038148</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.603173281893383</v>
+        <v>4.159403308638955</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09830496871110472</v>
+        <v>0.09847220606345053</v>
       </c>
       <c r="C20">
-        <v>225.4424537964668</v>
+        <v>222.4299573580581</v>
       </c>
       <c r="D20">
-        <v>204.9564537964668</v>
+        <v>204.7169573580581</v>
       </c>
       <c r="E20">
-        <v>-110.086</v>
+        <v>-107.313</v>
       </c>
       <c r="F20">
-        <v>49.914</v>
+        <v>52.687</v>
       </c>
       <c r="G20">
         <v>70.40000000000001</v>
@@ -2915,45 +2915,45 @@
         <v>12</v>
       </c>
       <c r="M20">
-        <v>2.8850292</v>
+        <v>3.2297131</v>
       </c>
       <c r="N20">
-        <v>9.1149708</v>
+        <v>8.7702869</v>
       </c>
       <c r="O20">
-        <v>3.099090072</v>
+        <v>2.981897546</v>
       </c>
       <c r="P20">
-        <v>6.015880728</v>
+        <v>5.788389354</v>
       </c>
       <c r="Q20">
-        <v>47.415880728</v>
+        <v>47.18838935399999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1115101569647619</v>
+        <v>0.1120804766215439</v>
       </c>
       <c r="T20">
-        <v>0.8564236255061073</v>
+        <v>0.863856802517396</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.34</v>
       </c>
       <c r="W20">
-        <v>0.038148</v>
+        <v>0.04045799999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.159403308638955</v>
+        <v>3.715500302488168</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09847220606345053</v>
+        <v>0.09822364341579634</v>
       </c>
       <c r="C21">
-        <v>222.4299573580581</v>
+        <v>220.0131203440763</v>
       </c>
       <c r="D21">
-        <v>204.7169573580581</v>
+        <v>205.0731203440762</v>
       </c>
       <c r="E21">
-        <v>-107.313</v>
+        <v>-104.54</v>
       </c>
       <c r="F21">
-        <v>52.687</v>
+        <v>55.46000000000001</v>
       </c>
       <c r="G21">
         <v>70.40000000000001</v>
@@ -2997,28 +2997,28 @@
         <v>12</v>
       </c>
       <c r="M21">
-        <v>3.2297131</v>
+        <v>3.399698</v>
       </c>
       <c r="N21">
-        <v>8.7702869</v>
+        <v>8.600301999999999</v>
       </c>
       <c r="O21">
-        <v>2.981897546</v>
+        <v>2.92410268</v>
       </c>
       <c r="P21">
-        <v>5.788389354</v>
+        <v>5.676199319999999</v>
       </c>
       <c r="Q21">
-        <v>47.18838935399999</v>
+        <v>47.07619932</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1120804766215439</v>
+        <v>0.1126650542697454</v>
       </c>
       <c r="T21">
-        <v>0.863856802517396</v>
+        <v>0.8714758089539671</v>
       </c>
       <c r="U21">
         <v>0.0613</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.715500302488168</v>
+        <v>3.529725287363759</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09822364341579634</v>
+        <v>0.09836316076814215</v>
       </c>
       <c r="C22">
-        <v>220.0131203440763</v>
+        <v>217.0400548603609</v>
       </c>
       <c r="D22">
-        <v>205.0731203440762</v>
+        <v>204.8730548603609</v>
       </c>
       <c r="E22">
-        <v>-104.54</v>
+        <v>-101.767</v>
       </c>
       <c r="F22">
-        <v>55.46000000000001</v>
+        <v>58.23300000000001</v>
       </c>
       <c r="G22">
         <v>70.40000000000001</v>
@@ -3079,45 +3079,45 @@
         <v>12</v>
       </c>
       <c r="M22">
-        <v>3.399698</v>
+        <v>3.732735300000001</v>
       </c>
       <c r="N22">
-        <v>8.600301999999999</v>
+        <v>8.267264699999998</v>
       </c>
       <c r="O22">
-        <v>2.92410268</v>
+        <v>2.810869998</v>
       </c>
       <c r="P22">
-        <v>5.676199319999999</v>
+        <v>5.456394701999999</v>
       </c>
       <c r="Q22">
-        <v>47.07619932</v>
+        <v>46.856394702</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1126650542697454</v>
+        <v>0.1132644313520787</v>
       </c>
       <c r="T22">
-        <v>0.8714758089539671</v>
+        <v>0.8792877016294387</v>
       </c>
       <c r="U22">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V22">
         <v>0.34</v>
       </c>
       <c r="W22">
-        <v>0.04045799999999999</v>
+        <v>0.042306</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.529725287363759</v>
+        <v>3.214800685170469</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09836316076814214</v>
+        <v>0.09813307812048792</v>
       </c>
       <c r="C23">
-        <v>217.040054860361</v>
+        <v>214.5971986981762</v>
       </c>
       <c r="D23">
-        <v>204.8730548603609</v>
+        <v>205.2031986981763</v>
       </c>
       <c r="E23">
-        <v>-101.767</v>
+        <v>-98.994</v>
       </c>
       <c r="F23">
-        <v>58.233</v>
+        <v>61.006</v>
       </c>
       <c r="G23">
         <v>70.40000000000001</v>
@@ -3161,28 +3161,28 @@
         <v>12</v>
       </c>
       <c r="M23">
-        <v>3.7327353</v>
+        <v>3.9104846</v>
       </c>
       <c r="N23">
-        <v>8.2672647</v>
+        <v>8.0895154</v>
       </c>
       <c r="O23">
-        <v>2.810869998</v>
+        <v>2.750435236</v>
       </c>
       <c r="P23">
-        <v>5.456394702</v>
+        <v>5.339080164</v>
       </c>
       <c r="Q23">
-        <v>46.856394702</v>
+        <v>46.739080164</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1132644313520786</v>
+        <v>0.1138791770775486</v>
       </c>
       <c r="T23">
-        <v>0.8792877016294386</v>
+        <v>0.8872998992453068</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.21480068517047</v>
+        <v>3.068673381299085</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09813307812048792</v>
+        <v>0.09908703547283375</v>
       </c>
       <c r="C24">
-        <v>214.5971986981762</v>
+        <v>210.4622662909777</v>
       </c>
       <c r="D24">
-        <v>205.2031986981763</v>
+        <v>203.8412662909777</v>
       </c>
       <c r="E24">
-        <v>-98.994</v>
+        <v>-96.221</v>
       </c>
       <c r="F24">
-        <v>61.006</v>
+        <v>63.779</v>
       </c>
       <c r="G24">
         <v>70.40000000000001</v>
@@ -3243,45 +3243,45 @@
         <v>12</v>
       </c>
       <c r="M24">
-        <v>3.9104846</v>
+        <v>4.585710100000001</v>
       </c>
       <c r="N24">
-        <v>8.0895154</v>
+        <v>7.414289899999999</v>
       </c>
       <c r="O24">
-        <v>2.750435236</v>
+        <v>2.520858566</v>
       </c>
       <c r="P24">
-        <v>5.339080164</v>
+        <v>4.893431333999999</v>
       </c>
       <c r="Q24">
-        <v>46.739080164</v>
+        <v>46.293431334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1138791770775486</v>
+        <v>0.1145098902244594</v>
       </c>
       <c r="T24">
-        <v>0.8872998992453068</v>
+        <v>0.8955202058901587</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.34</v>
       </c>
       <c r="W24">
-        <v>0.042306</v>
+        <v>0.047454</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.068673381299085</v>
+        <v>2.616824818472497</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09908703547283375</v>
+        <v>0.09890843282517957</v>
       </c>
       <c r="C25">
-        <v>210.4622662909777</v>
+        <v>207.9428740042708</v>
       </c>
       <c r="D25">
-        <v>203.8412662909777</v>
+        <v>204.0948740042709</v>
       </c>
       <c r="E25">
-        <v>-96.221</v>
+        <v>-93.44799999999999</v>
       </c>
       <c r="F25">
-        <v>63.779</v>
+        <v>66.55200000000001</v>
       </c>
       <c r="G25">
         <v>70.40000000000001</v>
@@ -3325,28 +3325,28 @@
         <v>12</v>
       </c>
       <c r="M25">
-        <v>4.585710100000001</v>
+        <v>4.7850888</v>
       </c>
       <c r="N25">
-        <v>7.414289899999999</v>
+        <v>7.2149112</v>
       </c>
       <c r="O25">
-        <v>2.520858566</v>
+        <v>2.453069808</v>
       </c>
       <c r="P25">
-        <v>4.893431333999999</v>
+        <v>4.761841391999999</v>
       </c>
       <c r="Q25">
-        <v>46.293431334</v>
+        <v>46.161841392</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1145098902244594</v>
+        <v>0.1151572010857626</v>
       </c>
       <c r="T25">
-        <v>0.8955202058901587</v>
+        <v>0.9039568363940856</v>
       </c>
       <c r="U25">
         <v>0.07190000000000001</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.616824818472497</v>
+        <v>2.507790451036144</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09890843282517957</v>
+        <v>0.09937333017752537</v>
       </c>
       <c r="C26">
-        <v>207.9428740042708</v>
+        <v>204.5110529785184</v>
       </c>
       <c r="D26">
-        <v>204.0948740042709</v>
+        <v>203.4360529785183</v>
       </c>
       <c r="E26">
-        <v>-93.44799999999999</v>
+        <v>-90.675</v>
       </c>
       <c r="F26">
-        <v>66.55200000000001</v>
+        <v>69.325</v>
       </c>
       <c r="G26">
         <v>70.40000000000001</v>
@@ -3407,45 +3407,45 @@
         <v>12</v>
       </c>
       <c r="M26">
-        <v>4.7850888</v>
+        <v>5.254835000000001</v>
       </c>
       <c r="N26">
-        <v>7.2149112</v>
+        <v>6.745164999999999</v>
       </c>
       <c r="O26">
-        <v>2.453069808</v>
+        <v>2.2933561</v>
       </c>
       <c r="P26">
-        <v>4.761841391999999</v>
+        <v>4.4518089</v>
       </c>
       <c r="Q26">
-        <v>46.161841392</v>
+        <v>45.85180889999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1151572010857626</v>
+        <v>0.1158217735700338</v>
       </c>
       <c r="T26">
-        <v>0.9039568363940855</v>
+        <v>0.9126184437114505</v>
       </c>
       <c r="U26">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V26">
         <v>0.34</v>
       </c>
       <c r="W26">
-        <v>0.047454</v>
+        <v>0.050028</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.507790451036144</v>
+        <v>2.283611188553018</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09937333017752537</v>
+        <v>0.09922046752987117</v>
       </c>
       <c r="C27">
-        <v>204.5110529785184</v>
+        <v>201.9542097201276</v>
       </c>
       <c r="D27">
-        <v>203.4360529785183</v>
+        <v>203.6522097201276</v>
       </c>
       <c r="E27">
-        <v>-90.675</v>
+        <v>-87.902</v>
       </c>
       <c r="F27">
-        <v>69.325</v>
+        <v>72.098</v>
       </c>
       <c r="G27">
         <v>70.40000000000001</v>
@@ -3489,28 +3489,28 @@
         <v>12</v>
       </c>
       <c r="M27">
-        <v>5.254835000000001</v>
+        <v>5.4650284</v>
       </c>
       <c r="N27">
-        <v>6.745164999999999</v>
+        <v>6.5349716</v>
       </c>
       <c r="O27">
-        <v>2.2933561</v>
+        <v>2.221890344</v>
       </c>
       <c r="P27">
-        <v>4.4518089</v>
+        <v>4.313081255999999</v>
       </c>
       <c r="Q27">
-        <v>45.85180889999999</v>
+        <v>45.713081256</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1158217735700338</v>
+        <v>0.1165043074727989</v>
       </c>
       <c r="T27">
-        <v>0.9126184437114505</v>
+        <v>0.9215141485238795</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.283611188553018</v>
+        <v>2.195779988993287</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09922046752987117</v>
+        <v>0.09906760488221697</v>
       </c>
       <c r="C28">
-        <v>201.9542097201276</v>
+        <v>199.397826296013</v>
       </c>
       <c r="D28">
-        <v>203.6522097201276</v>
+        <v>203.868826296013</v>
       </c>
       <c r="E28">
-        <v>-87.902</v>
+        <v>-85.12899999999999</v>
       </c>
       <c r="F28">
-        <v>72.098</v>
+        <v>74.87100000000001</v>
       </c>
       <c r="G28">
         <v>70.40000000000001</v>
@@ -3571,28 +3571,28 @@
         <v>12</v>
       </c>
       <c r="M28">
-        <v>5.4650284</v>
+        <v>5.675221800000001</v>
       </c>
       <c r="N28">
-        <v>6.5349716</v>
+        <v>6.324778199999999</v>
       </c>
       <c r="O28">
-        <v>2.221890344</v>
+        <v>2.150424588</v>
       </c>
       <c r="P28">
-        <v>4.313081255999999</v>
+        <v>4.174353611999999</v>
       </c>
       <c r="Q28">
-        <v>45.713081256</v>
+        <v>45.574353612</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1165043074727989</v>
+        <v>0.1172055409345438</v>
       </c>
       <c r="T28">
-        <v>0.9215141485238795</v>
+        <v>0.9306535712763747</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.195779988993287</v>
+        <v>2.114454804215757</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09906760488221697</v>
+        <v>0.09891474223456279</v>
       </c>
       <c r="C29">
-        <v>199.397826296013</v>
+        <v>196.8419041750579</v>
       </c>
       <c r="D29">
-        <v>203.868826296013</v>
+        <v>204.085904175058</v>
       </c>
       <c r="E29">
-        <v>-85.12899999999999</v>
+        <v>-82.35599999999999</v>
       </c>
       <c r="F29">
-        <v>74.87100000000001</v>
+        <v>77.64400000000001</v>
       </c>
       <c r="G29">
         <v>70.40000000000001</v>
@@ -3653,28 +3653,28 @@
         <v>12</v>
       </c>
       <c r="M29">
-        <v>5.675221800000001</v>
+        <v>5.885415200000001</v>
       </c>
       <c r="N29">
-        <v>6.324778199999999</v>
+        <v>6.114584799999999</v>
       </c>
       <c r="O29">
-        <v>2.150424588</v>
+        <v>2.078958832</v>
       </c>
       <c r="P29">
-        <v>4.174353611999999</v>
+        <v>4.035625968</v>
       </c>
       <c r="Q29">
-        <v>45.574353612</v>
+        <v>45.435625968</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1172055409345438</v>
+        <v>0.1179262531035594</v>
       </c>
       <c r="T29">
-        <v>0.9306535712763747</v>
+        <v>0.9400468668831061</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.114454804215757</v>
+        <v>2.038938561208052</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09891474223456279</v>
+        <v>0.1014797595869086</v>
       </c>
       <c r="C30">
-        <v>196.8419041750579</v>
+        <v>190.4864914688479</v>
       </c>
       <c r="D30">
-        <v>204.085904175058</v>
+        <v>200.5034914688479</v>
       </c>
       <c r="E30">
-        <v>-82.35599999999999</v>
+        <v>-79.58299999999998</v>
       </c>
       <c r="F30">
-        <v>77.64400000000001</v>
+        <v>80.41700000000002</v>
       </c>
       <c r="G30">
         <v>70.40000000000001</v>
@@ -3735,45 +3735,45 @@
         <v>12</v>
       </c>
       <c r="M30">
-        <v>5.885415200000001</v>
+        <v>7.237530000000001</v>
       </c>
       <c r="N30">
-        <v>6.114584799999999</v>
+        <v>4.762469999999999</v>
       </c>
       <c r="O30">
-        <v>2.078958832</v>
+        <v>1.6192398</v>
       </c>
       <c r="P30">
-        <v>4.035625968</v>
+        <v>3.143230199999999</v>
       </c>
       <c r="Q30">
-        <v>45.435625968</v>
+        <v>44.5432302</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1179262531035594</v>
+        <v>0.1186672670238149</v>
       </c>
       <c r="T30">
-        <v>0.9400468668831061</v>
+        <v>0.9497047623660835</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0.34</v>
       </c>
       <c r="W30">
-        <v>0.050028</v>
+        <v>0.05939999999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.038938561208052</v>
+        <v>1.658024215443666</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1014797595869086</v>
+        <v>0.1014206169392544</v>
       </c>
       <c r="C31">
-        <v>190.4864914688479</v>
+        <v>187.7946755374234</v>
       </c>
       <c r="D31">
-        <v>200.5034914688479</v>
+        <v>200.5846755374234</v>
       </c>
       <c r="E31">
-        <v>-79.583</v>
+        <v>-76.81</v>
       </c>
       <c r="F31">
-        <v>80.417</v>
+        <v>83.19</v>
       </c>
       <c r="G31">
         <v>70.40000000000001</v>
@@ -3817,28 +3817,28 @@
         <v>12</v>
       </c>
       <c r="M31">
-        <v>7.23753</v>
+        <v>7.4871</v>
       </c>
       <c r="N31">
-        <v>4.76247</v>
+        <v>4.5129</v>
       </c>
       <c r="O31">
-        <v>1.6192398</v>
+        <v>1.534386</v>
       </c>
       <c r="P31">
-        <v>3.1432302</v>
+        <v>2.978514</v>
       </c>
       <c r="Q31">
-        <v>44.5432302</v>
+        <v>44.378514</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1186672670238149</v>
+        <v>0.1194294527703634</v>
       </c>
       <c r="T31">
-        <v>0.9497047623660835</v>
+        <v>0.959638597720003</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.658024215443667</v>
+        <v>1.602756741595544</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1014206169392544</v>
+        <v>0.1013614742916002</v>
       </c>
       <c r="C32">
-        <v>187.7946755374234</v>
+        <v>185.1029253756537</v>
       </c>
       <c r="D32">
-        <v>200.5846755374234</v>
+        <v>200.6659253756537</v>
       </c>
       <c r="E32">
-        <v>-76.81</v>
+        <v>-74.03699999999999</v>
       </c>
       <c r="F32">
-        <v>83.19</v>
+        <v>85.96300000000001</v>
       </c>
       <c r="G32">
         <v>70.40000000000001</v>
@@ -3899,28 +3899,28 @@
         <v>12</v>
       </c>
       <c r="M32">
-        <v>7.4871</v>
+        <v>7.73667</v>
       </c>
       <c r="N32">
-        <v>4.5129</v>
+        <v>4.26333</v>
       </c>
       <c r="O32">
-        <v>1.534386</v>
+        <v>1.4495322</v>
       </c>
       <c r="P32">
-        <v>2.978514</v>
+        <v>2.8137978</v>
       </c>
       <c r="Q32">
-        <v>44.378514</v>
+        <v>44.21379779999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1194294527703634</v>
+        <v>0.1202137308573916</v>
       </c>
       <c r="T32">
-        <v>0.959638597720003</v>
+        <v>0.9698603703305579</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.602756741595544</v>
+        <v>1.551054911221494</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1013614742916002</v>
+        <v>0.101302331643946</v>
       </c>
       <c r="C33">
-        <v>185.1029253756537</v>
+        <v>182.4112410634942</v>
       </c>
       <c r="D33">
-        <v>200.6659253756537</v>
+        <v>200.7472410634942</v>
       </c>
       <c r="E33">
-        <v>-74.03699999999999</v>
+        <v>-71.264</v>
       </c>
       <c r="F33">
-        <v>85.96300000000001</v>
+        <v>88.736</v>
       </c>
       <c r="G33">
         <v>70.40000000000001</v>
@@ -3981,28 +3981,28 @@
         <v>12</v>
       </c>
       <c r="M33">
-        <v>7.73667</v>
+        <v>7.98624</v>
       </c>
       <c r="N33">
-        <v>4.26333</v>
+        <v>4.01376</v>
       </c>
       <c r="O33">
-        <v>1.4495322</v>
+        <v>1.3646784</v>
       </c>
       <c r="P33">
-        <v>2.8137978</v>
+        <v>2.6490816</v>
       </c>
       <c r="Q33">
-        <v>44.21379779999999</v>
+        <v>44.0490816</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1202137308573916</v>
+        <v>0.1210210759469794</v>
       </c>
       <c r="T33">
-        <v>0.9698603703305579</v>
+        <v>0.9803827833120115</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.551054911221494</v>
+        <v>1.502584445245823</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.101302331643946</v>
+        <v>0.1160590777366767</v>
       </c>
       <c r="C34">
-        <v>182.4112410634942</v>
+        <v>161.2046582109588</v>
       </c>
       <c r="D34">
-        <v>200.7472410634942</v>
+        <v>182.3136582109588</v>
       </c>
       <c r="E34">
-        <v>-71.264</v>
+        <v>-68.49099999999999</v>
       </c>
       <c r="F34">
-        <v>88.736</v>
+        <v>91.50900000000001</v>
       </c>
       <c r="G34">
         <v>70.40000000000001</v>
@@ -4063,45 +4063,45 @@
         <v>12</v>
       </c>
       <c r="M34">
-        <v>7.98624</v>
+        <v>13.4335212</v>
       </c>
       <c r="N34">
-        <v>4.01376</v>
+        <v>-1.433521200000003</v>
       </c>
       <c r="O34">
-        <v>1.3646784</v>
+        <v>-0.4873972080000011</v>
       </c>
       <c r="P34">
-        <v>2.6490816</v>
+        <v>-0.946123992000002</v>
       </c>
       <c r="Q34">
-        <v>44.0490816</v>
+        <v>40.45387600799999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1210210759469794</v>
+        <v>0.122878186006752</v>
       </c>
       <c r="T34">
-        <v>0.9803827833120115</v>
+        <v>1.004587152983616</v>
       </c>
       <c r="U34">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.34</v>
+        <v>0.3037178368393835</v>
       </c>
       <c r="W34">
-        <v>0.05939999999999999</v>
+        <v>0.1022142215519785</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.502584445245823</v>
+        <v>0.8932877554099514</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1160590777366767</v>
+        <v>0.1170690777366767</v>
       </c>
       <c r="C35">
-        <v>161.2046582109588</v>
+        <v>157.2930108733984</v>
       </c>
       <c r="D35">
-        <v>182.3136582109588</v>
+        <v>181.1750108733984</v>
       </c>
       <c r="E35">
-        <v>-68.49099999999999</v>
+        <v>-65.71799999999999</v>
       </c>
       <c r="F35">
-        <v>91.50900000000001</v>
+        <v>94.28200000000001</v>
       </c>
       <c r="G35">
         <v>70.40000000000001</v>
@@ -4145,37 +4145,37 @@
         <v>12</v>
       </c>
       <c r="M35">
-        <v>13.4335212</v>
+        <v>13.8405976</v>
       </c>
       <c r="N35">
-        <v>-1.433521200000003</v>
+        <v>-1.840597600000002</v>
       </c>
       <c r="O35">
-        <v>-0.4873972080000011</v>
+        <v>-0.6258031840000009</v>
       </c>
       <c r="P35">
-        <v>-0.946123992000002</v>
+        <v>-1.214794416000001</v>
       </c>
       <c r="Q35">
-        <v>40.45387600799999</v>
+        <v>40.18520558399999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.122878186006752</v>
+        <v>0.1240460373098846</v>
       </c>
       <c r="T35">
-        <v>1.004587152983616</v>
+        <v>1.019808170453065</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.3037178368393835</v>
+        <v>0.294784959285284</v>
       </c>
       <c r="W35">
-        <v>0.1022142215519785</v>
+        <v>0.1035255679769203</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8932877554099514</v>
+        <v>0.8670145861331882</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1170690777366767</v>
+        <v>0.1180790777366767</v>
       </c>
       <c r="C36">
-        <v>157.2930108733984</v>
+        <v>153.3954981934043</v>
       </c>
       <c r="D36">
-        <v>181.1750108733984</v>
+        <v>180.0504981934043</v>
       </c>
       <c r="E36">
-        <v>-65.71799999999999</v>
+        <v>-62.94499999999999</v>
       </c>
       <c r="F36">
-        <v>94.28200000000001</v>
+        <v>97.05500000000001</v>
       </c>
       <c r="G36">
         <v>70.40000000000001</v>
@@ -4227,37 +4227,37 @@
         <v>12</v>
       </c>
       <c r="M36">
-        <v>13.8405976</v>
+        <v>14.247674</v>
       </c>
       <c r="N36">
-        <v>-1.840597600000002</v>
+        <v>-2.247674000000002</v>
       </c>
       <c r="O36">
-        <v>-0.6258031840000009</v>
+        <v>-0.7642091600000006</v>
       </c>
       <c r="P36">
-        <v>-1.214794416000001</v>
+        <v>-1.483464840000001</v>
       </c>
       <c r="Q36">
-        <v>40.18520558399999</v>
+        <v>39.91653516</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1240460373098846</v>
+        <v>0.1252498224992674</v>
       </c>
       <c r="T36">
-        <v>1.019808170453065</v>
+        <v>1.035497526921573</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.294784959285284</v>
+        <v>0.2863625318771331</v>
       </c>
       <c r="W36">
-        <v>0.1035255679769203</v>
+        <v>0.1047619803204369</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8670145861331882</v>
+        <v>0.8422427408150972</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1180790777366767</v>
+        <v>0.1190890777366767</v>
       </c>
       <c r="C37">
-        <v>153.3954981934043</v>
+        <v>149.51185860252</v>
       </c>
       <c r="D37">
-        <v>180.0504981934043</v>
+        <v>178.93985860252</v>
       </c>
       <c r="E37">
-        <v>-62.94499999999999</v>
+        <v>-60.17199999999998</v>
       </c>
       <c r="F37">
-        <v>97.05500000000001</v>
+        <v>99.82800000000002</v>
       </c>
       <c r="G37">
         <v>70.40000000000001</v>
@@ -4309,37 +4309,37 @@
         <v>12</v>
       </c>
       <c r="M37">
-        <v>14.247674</v>
+        <v>14.6547504</v>
       </c>
       <c r="N37">
-        <v>-2.247674000000002</v>
+        <v>-2.654750400000005</v>
       </c>
       <c r="O37">
-        <v>-0.7642091600000006</v>
+        <v>-0.9026151360000016</v>
       </c>
       <c r="P37">
-        <v>-1.483464840000001</v>
+        <v>-1.752135264000003</v>
       </c>
       <c r="Q37">
-        <v>39.91653516</v>
+        <v>39.647864736</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1252498224992674</v>
+        <v>0.1264912259758185</v>
       </c>
       <c r="T37">
-        <v>1.035497526921573</v>
+        <v>1.051677175779723</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.2863625318771331</v>
+        <v>0.2784080171027682</v>
       </c>
       <c r="W37">
-        <v>0.1047619803204369</v>
+        <v>0.1059297030893136</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8422427408150972</v>
+        <v>0.8188471091257887</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1190890777366767</v>
+        <v>0.1416260679468124</v>
       </c>
       <c r="C38">
-        <v>149.51185860252</v>
+        <v>125.0890256911013</v>
       </c>
       <c r="D38">
-        <v>178.93985860252</v>
+        <v>157.2900256911013</v>
       </c>
       <c r="E38">
-        <v>-60.172</v>
+        <v>-57.399</v>
       </c>
       <c r="F38">
-        <v>99.828</v>
+        <v>102.601</v>
       </c>
       <c r="G38">
         <v>70.40000000000001</v>
@@ -4391,45 +4391,45 @@
         <v>12</v>
       </c>
       <c r="M38">
-        <v>14.6547504</v>
+        <v>20.6022808</v>
       </c>
       <c r="N38">
-        <v>-2.654750400000001</v>
+        <v>-8.602280799999999</v>
       </c>
       <c r="O38">
-        <v>-0.9026151360000004</v>
+        <v>-2.924775472</v>
       </c>
       <c r="P38">
-        <v>-1.752135264000001</v>
+        <v>-5.677505327999999</v>
       </c>
       <c r="Q38">
-        <v>39.647864736</v>
+        <v>35.722494672</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1264912259758185</v>
+        <v>0.1302275791026341</v>
       </c>
       <c r="T38">
-        <v>1.051677175779723</v>
+        <v>1.10037438240418</v>
       </c>
       <c r="U38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.2784080171027682</v>
+        <v>0.1980363261527821</v>
       </c>
       <c r="W38">
-        <v>0.1059297030893136</v>
+        <v>0.1610343057085214</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.818847109125789</v>
+        <v>0.5824597828023003</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1416260679468124</v>
+        <v>0.1431760679468124</v>
       </c>
       <c r="C39">
-        <v>125.0890256911013</v>
+        <v>121.0179932441291</v>
       </c>
       <c r="D39">
-        <v>157.2900256911013</v>
+        <v>155.9919932441291</v>
       </c>
       <c r="E39">
-        <v>-57.399</v>
+        <v>-54.62599999999999</v>
       </c>
       <c r="F39">
-        <v>102.601</v>
+        <v>105.374</v>
       </c>
       <c r="G39">
         <v>70.40000000000001</v>
@@ -4473,37 +4473,37 @@
         <v>12</v>
       </c>
       <c r="M39">
-        <v>20.6022808</v>
+        <v>21.1590992</v>
       </c>
       <c r="N39">
-        <v>-8.602280799999999</v>
+        <v>-9.159099200000004</v>
       </c>
       <c r="O39">
-        <v>-2.924775472</v>
+        <v>-3.114093728000002</v>
       </c>
       <c r="P39">
-        <v>-5.677505327999999</v>
+        <v>-6.045005472000001</v>
       </c>
       <c r="Q39">
-        <v>35.722494672</v>
+        <v>35.354994528</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1302275791026341</v>
+        <v>0.1315893142494508</v>
       </c>
       <c r="T39">
-        <v>1.10037438240418</v>
+        <v>1.118122356313925</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1980363261527821</v>
+        <v>0.1928248438856036</v>
       </c>
       <c r="W39">
-        <v>0.1610343057085214</v>
+        <v>0.1620807713477708</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5824597828023003</v>
+        <v>0.5671318937811869</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1431760679468124</v>
+        <v>0.1447260679468124</v>
       </c>
       <c r="C40">
-        <v>121.0179932441291</v>
+        <v>116.9682094113738</v>
       </c>
       <c r="D40">
-        <v>155.9919932441291</v>
+        <v>154.7152094113738</v>
       </c>
       <c r="E40">
-        <v>-54.62599999999999</v>
+        <v>-51.85299999999999</v>
       </c>
       <c r="F40">
-        <v>105.374</v>
+        <v>108.147</v>
       </c>
       <c r="G40">
         <v>70.40000000000001</v>
@@ -4555,37 +4555,37 @@
         <v>12</v>
       </c>
       <c r="M40">
-        <v>21.1590992</v>
+        <v>21.7159176</v>
       </c>
       <c r="N40">
-        <v>-9.159099200000004</v>
+        <v>-9.715917600000001</v>
       </c>
       <c r="O40">
-        <v>-3.114093728000002</v>
+        <v>-3.303411984000001</v>
       </c>
       <c r="P40">
-        <v>-6.045005472000001</v>
+        <v>-6.412505616000001</v>
       </c>
       <c r="Q40">
-        <v>35.354994528</v>
+        <v>34.987494384</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1315893142494508</v>
+        <v>0.1329956964502615</v>
       </c>
       <c r="T40">
-        <v>1.118122356313925</v>
+        <v>1.136452231007596</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1928248438856036</v>
+        <v>0.1878806171193061</v>
       </c>
       <c r="W40">
-        <v>0.1620807713477708</v>
+        <v>0.1630735720824434</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5671318937811869</v>
+        <v>0.5525900503509003</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1447260679468124</v>
+        <v>0.1462760679468124</v>
       </c>
       <c r="C41">
-        <v>116.9682094113738</v>
+        <v>112.93915667332</v>
       </c>
       <c r="D41">
-        <v>154.7152094113738</v>
+        <v>153.45915667332</v>
       </c>
       <c r="E41">
-        <v>-51.85299999999999</v>
+        <v>-49.07999999999998</v>
       </c>
       <c r="F41">
-        <v>108.147</v>
+        <v>110.92</v>
       </c>
       <c r="G41">
         <v>70.40000000000001</v>
@@ -4637,37 +4637,37 @@
         <v>12</v>
       </c>
       <c r="M41">
-        <v>21.7159176</v>
+        <v>22.27273600000001</v>
       </c>
       <c r="N41">
-        <v>-9.715917600000001</v>
+        <v>-10.27273600000001</v>
       </c>
       <c r="O41">
-        <v>-3.303411984000001</v>
+        <v>-3.492730240000002</v>
       </c>
       <c r="P41">
-        <v>-6.412505616000001</v>
+        <v>-6.780005760000003</v>
       </c>
       <c r="Q41">
-        <v>34.987494384</v>
+        <v>34.61999424</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1329956964502615</v>
+        <v>0.1344489580577658</v>
       </c>
       <c r="T41">
-        <v>1.136452231007596</v>
+        <v>1.155393101524389</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1878806171193061</v>
+        <v>0.1831836016913234</v>
       </c>
       <c r="W41">
-        <v>0.1630735720824434</v>
+        <v>0.1640167327803823</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5525900503509003</v>
+        <v>0.5387752990921275</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1462760679468124</v>
+        <v>0.1478260679468124</v>
       </c>
       <c r="C42">
-        <v>112.93915667332</v>
+        <v>108.9303341810055</v>
       </c>
       <c r="D42">
-        <v>153.45915667332</v>
+        <v>152.2233341810055</v>
       </c>
       <c r="E42">
-        <v>-49.07999999999998</v>
+        <v>-46.30699999999999</v>
       </c>
       <c r="F42">
-        <v>110.92</v>
+        <v>113.693</v>
       </c>
       <c r="G42">
         <v>70.40000000000001</v>
@@ -4719,37 +4719,37 @@
         <v>12</v>
       </c>
       <c r="M42">
-        <v>22.27273600000001</v>
+        <v>22.8295544</v>
       </c>
       <c r="N42">
-        <v>-10.27273600000001</v>
+        <v>-10.8295544</v>
       </c>
       <c r="O42">
-        <v>-3.492730240000002</v>
+        <v>-3.682048496000001</v>
       </c>
       <c r="P42">
-        <v>-6.780005760000003</v>
+        <v>-7.147505904000002</v>
       </c>
       <c r="Q42">
-        <v>34.61999424</v>
+        <v>34.252494096</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1344489580577658</v>
+        <v>0.1359514827706093</v>
       </c>
       <c r="T42">
-        <v>1.155393101524389</v>
+        <v>1.174976035448532</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1831836016913234</v>
+        <v>0.1787157089671448</v>
       </c>
       <c r="W42">
-        <v>0.1640167327803823</v>
+        <v>0.1649138856393974</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5387752990921275</v>
+        <v>0.5256344381386611</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1478260679468124</v>
+        <v>0.1493760679468124</v>
       </c>
       <c r="C43">
-        <v>108.9303341810055</v>
+        <v>104.9412570901351</v>
       </c>
       <c r="D43">
-        <v>152.2233341810055</v>
+        <v>151.0072570901351</v>
       </c>
       <c r="E43">
-        <v>-46.30699999999999</v>
+        <v>-43.53399999999998</v>
       </c>
       <c r="F43">
-        <v>113.693</v>
+        <v>116.466</v>
       </c>
       <c r="G43">
         <v>70.40000000000001</v>
@@ -4801,37 +4801,37 @@
         <v>12</v>
       </c>
       <c r="M43">
-        <v>22.8295544</v>
+        <v>23.3863728</v>
       </c>
       <c r="N43">
-        <v>-10.8295544</v>
+        <v>-11.3863728</v>
       </c>
       <c r="O43">
-        <v>-3.682048496000001</v>
+        <v>-3.871366752000001</v>
       </c>
       <c r="P43">
-        <v>-7.147505904000002</v>
+        <v>-7.515006048000002</v>
       </c>
       <c r="Q43">
-        <v>34.252494096</v>
+        <v>33.88499395199999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1359514827706093</v>
+        <v>0.1375058186804474</v>
       </c>
       <c r="T43">
-        <v>1.174976035448532</v>
+        <v>1.195234242956265</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1787157089671448</v>
+        <v>0.1744605730393556</v>
       </c>
       <c r="W43">
-        <v>0.1649138856393974</v>
+        <v>0.1657683169336974</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5256344381386611</v>
+        <v>0.5131193324686929</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1493760679468124</v>
+        <v>0.1509260679468124</v>
       </c>
       <c r="C44">
-        <v>104.9412570901351</v>
+        <v>100.9714559268596</v>
       </c>
       <c r="D44">
-        <v>151.0072570901351</v>
+        <v>149.8104559268596</v>
       </c>
       <c r="E44">
-        <v>-43.53400000000001</v>
+        <v>-40.761</v>
       </c>
       <c r="F44">
-        <v>116.466</v>
+        <v>119.239</v>
       </c>
       <c r="G44">
         <v>70.40000000000001</v>
@@ -4883,37 +4883,37 @@
         <v>12</v>
       </c>
       <c r="M44">
-        <v>23.3863728</v>
+        <v>23.9431912</v>
       </c>
       <c r="N44">
-        <v>-11.3863728</v>
+        <v>-11.9431912</v>
       </c>
       <c r="O44">
-        <v>-3.871366752</v>
+        <v>-4.060685008000001</v>
       </c>
       <c r="P44">
-        <v>-7.515006048</v>
+        <v>-7.882506192</v>
       </c>
       <c r="Q44">
-        <v>33.884993952</v>
+        <v>33.517493808</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1375058186804474</v>
+        <v>0.1391146926923851</v>
       </c>
       <c r="T44">
-        <v>1.195234242956265</v>
+        <v>1.216203264762515</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1744605730393556</v>
+        <v>0.1704033504105334</v>
       </c>
       <c r="W44">
-        <v>0.1657683169336974</v>
+        <v>0.1665830072375649</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5131193324686931</v>
+        <v>0.501186324736863</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1509260679468124</v>
+        <v>0.1685002971821717</v>
       </c>
       <c r="C45">
-        <v>100.9714559268596</v>
+        <v>85.84637892766929</v>
       </c>
       <c r="D45">
-        <v>149.8104559268596</v>
+        <v>137.4583789276693</v>
       </c>
       <c r="E45">
-        <v>-40.761</v>
+        <v>-37.988</v>
       </c>
       <c r="F45">
-        <v>119.239</v>
+        <v>122.012</v>
       </c>
       <c r="G45">
         <v>70.40000000000001</v>
@@ -4965,45 +4965,45 @@
         <v>12</v>
       </c>
       <c r="M45">
-        <v>23.9431912</v>
+        <v>28.7704296</v>
       </c>
       <c r="N45">
-        <v>-11.9431912</v>
+        <v>-16.7704296</v>
       </c>
       <c r="O45">
-        <v>-4.060685008000001</v>
+        <v>-5.701946064</v>
       </c>
       <c r="P45">
-        <v>-7.882506192</v>
+        <v>-11.068483536</v>
       </c>
       <c r="Q45">
-        <v>33.517493808</v>
+        <v>30.331516464</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1391146926923851</v>
+        <v>0.141895721553605</v>
       </c>
       <c r="T45">
-        <v>1.216203264762515</v>
+        <v>1.252449393671328</v>
       </c>
       <c r="U45">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.1704033504105334</v>
+        <v>0.1418122724173712</v>
       </c>
       <c r="W45">
-        <v>0.1665830072375649</v>
+        <v>0.2023606661639839</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.501186324736863</v>
+        <v>0.4170949188746211</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1685002971821717</v>
+        <v>0.1704002971821717</v>
       </c>
       <c r="C46">
-        <v>85.84637892766929</v>
+        <v>81.85889373145862</v>
       </c>
       <c r="D46">
-        <v>137.4583789276693</v>
+        <v>136.2438937314586</v>
       </c>
       <c r="E46">
-        <v>-37.988</v>
+        <v>-35.21499999999999</v>
       </c>
       <c r="F46">
-        <v>122.012</v>
+        <v>124.785</v>
       </c>
       <c r="G46">
         <v>70.40000000000001</v>
@@ -5047,37 +5047,37 @@
         <v>12</v>
       </c>
       <c r="M46">
-        <v>28.7704296</v>
+        <v>29.42430300000001</v>
       </c>
       <c r="N46">
-        <v>-16.7704296</v>
+        <v>-17.42430300000001</v>
       </c>
       <c r="O46">
-        <v>-5.701946064</v>
+        <v>-5.924263020000002</v>
       </c>
       <c r="P46">
-        <v>-11.068483536</v>
+        <v>-11.50003998</v>
       </c>
       <c r="Q46">
-        <v>30.331516464</v>
+        <v>29.89996001999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.141895721553605</v>
+        <v>0.1436429164909433</v>
       </c>
       <c r="T46">
-        <v>1.252449393671328</v>
+        <v>1.275221200828988</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.1418122724173712</v>
+        <v>0.1386608885858741</v>
       </c>
       <c r="W46">
-        <v>0.2023606661639839</v>
+        <v>0.2031037624714509</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4170949188746211</v>
+        <v>0.4078261428996295</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1704002971821717</v>
+        <v>0.1723002971821717</v>
       </c>
       <c r="C47">
-        <v>81.85889373145862</v>
+        <v>77.89268125217255</v>
       </c>
       <c r="D47">
-        <v>136.2438937314586</v>
+        <v>135.0506812521726</v>
       </c>
       <c r="E47">
-        <v>-35.21499999999999</v>
+        <v>-32.44199999999999</v>
       </c>
       <c r="F47">
-        <v>124.785</v>
+        <v>127.558</v>
       </c>
       <c r="G47">
         <v>70.40000000000001</v>
@@ -5129,37 +5129,37 @@
         <v>12</v>
       </c>
       <c r="M47">
-        <v>29.42430300000001</v>
+        <v>30.0781764</v>
       </c>
       <c r="N47">
-        <v>-17.42430300000001</v>
+        <v>-18.0781764</v>
       </c>
       <c r="O47">
-        <v>-5.924263020000002</v>
+        <v>-6.146579976000002</v>
       </c>
       <c r="P47">
-        <v>-11.50003998</v>
+        <v>-11.931596424</v>
       </c>
       <c r="Q47">
-        <v>29.89996001999999</v>
+        <v>29.468403576</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1436429164909433</v>
+        <v>0.1454548223518867</v>
       </c>
       <c r="T47">
-        <v>1.275221200828988</v>
+        <v>1.298836408251748</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.1386608885858741</v>
+        <v>0.1356465214427029</v>
       </c>
       <c r="W47">
-        <v>0.2031037624714509</v>
+        <v>0.2038145502438107</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4078261428996295</v>
+        <v>0.3989603571844202</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1723002971821717</v>
+        <v>0.1742002971821717</v>
       </c>
       <c r="C48">
-        <v>77.89268125217255</v>
+        <v>73.94718742827703</v>
       </c>
       <c r="D48">
-        <v>135.0506812521726</v>
+        <v>133.878187428277</v>
       </c>
       <c r="E48">
-        <v>-32.44199999999999</v>
+        <v>-29.66899999999998</v>
       </c>
       <c r="F48">
-        <v>127.558</v>
+        <v>130.331</v>
       </c>
       <c r="G48">
         <v>70.40000000000001</v>
@@ -5211,37 +5211,37 @@
         <v>12</v>
       </c>
       <c r="M48">
-        <v>30.0781764</v>
+        <v>30.73204980000001</v>
       </c>
       <c r="N48">
-        <v>-18.0781764</v>
+        <v>-18.73204980000001</v>
       </c>
       <c r="O48">
-        <v>-6.146579976000002</v>
+        <v>-6.368896932000003</v>
       </c>
       <c r="P48">
-        <v>-11.931596424</v>
+        <v>-12.363152868</v>
       </c>
       <c r="Q48">
-        <v>29.468403576</v>
+        <v>29.03684713199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1454548223518867</v>
+        <v>0.1473351020189034</v>
       </c>
       <c r="T48">
-        <v>1.298836408251748</v>
+        <v>1.323342755577252</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1356465214427029</v>
+        <v>0.1327604252417943</v>
       </c>
       <c r="W48">
-        <v>0.2038145502438107</v>
+        <v>0.2044950917279849</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3989603571844202</v>
+        <v>0.3904718389464538</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1742002971821717</v>
+        <v>0.1761002971821717</v>
       </c>
       <c r="C49">
-        <v>73.94718742827703</v>
+        <v>70.02187727380928</v>
       </c>
       <c r="D49">
-        <v>133.878187428277</v>
+        <v>132.7258772738093</v>
       </c>
       <c r="E49">
-        <v>-29.66899999999998</v>
+        <v>-26.89599999999999</v>
       </c>
       <c r="F49">
-        <v>130.331</v>
+        <v>133.104</v>
       </c>
       <c r="G49">
         <v>70.40000000000001</v>
@@ -5293,37 +5293,37 @@
         <v>12</v>
       </c>
       <c r="M49">
-        <v>30.73204980000001</v>
+        <v>31.3859232</v>
       </c>
       <c r="N49">
-        <v>-18.73204980000001</v>
+        <v>-19.3859232</v>
       </c>
       <c r="O49">
-        <v>-6.368896932000003</v>
+        <v>-6.591213888000002</v>
       </c>
       <c r="P49">
-        <v>-12.363152868</v>
+        <v>-12.794709312</v>
       </c>
       <c r="Q49">
-        <v>29.03684713199999</v>
+        <v>28.605290688</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1473351020189034</v>
+        <v>0.1492877001346515</v>
       </c>
       <c r="T49">
-        <v>1.323342755577252</v>
+        <v>1.348791654722969</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1327604252417943</v>
+        <v>0.1299945830492569</v>
       </c>
       <c r="W49">
-        <v>0.2044950917279849</v>
+        <v>0.2051472773169852</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3904718389464538</v>
+        <v>0.3823370089684027</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1761002971821717</v>
+        <v>0.1780002971821717</v>
       </c>
       <c r="C50">
-        <v>70.02187727380931</v>
+        <v>66.11623406445193</v>
       </c>
       <c r="D50">
-        <v>132.7258772738093</v>
+        <v>131.5932340644519</v>
       </c>
       <c r="E50">
-        <v>-26.89599999999999</v>
+        <v>-24.12299999999999</v>
       </c>
       <c r="F50">
-        <v>133.104</v>
+        <v>135.877</v>
       </c>
       <c r="G50">
         <v>70.40000000000001</v>
@@ -5375,37 +5375,37 @@
         <v>12</v>
       </c>
       <c r="M50">
-        <v>31.3859232</v>
+        <v>32.0397966</v>
       </c>
       <c r="N50">
-        <v>-19.3859232</v>
+        <v>-20.0397966</v>
       </c>
       <c r="O50">
-        <v>-6.591213888000002</v>
+        <v>-6.813530844000002</v>
       </c>
       <c r="P50">
-        <v>-12.794709312</v>
+        <v>-13.226265756</v>
       </c>
       <c r="Q50">
-        <v>28.605290688</v>
+        <v>28.173734244</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1492877001346515</v>
+        <v>0.151316870725527</v>
       </c>
       <c r="T50">
-        <v>1.348791654722969</v>
+        <v>1.375238549913615</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1299945830492569</v>
+        <v>0.1273416323747823</v>
       </c>
       <c r="W50">
-        <v>0.2051472773169852</v>
+        <v>0.2057728430860264</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3823370089684027</v>
+        <v>0.3745342128670067</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1780002971821717</v>
+        <v>0.1799002971821717</v>
       </c>
       <c r="C51">
-        <v>66.11623406445193</v>
+        <v>62.22975856492835</v>
       </c>
       <c r="D51">
-        <v>131.5932340644519</v>
+        <v>130.4797585649283</v>
       </c>
       <c r="E51">
-        <v>-24.12299999999999</v>
+        <v>-21.34999999999999</v>
       </c>
       <c r="F51">
-        <v>135.877</v>
+        <v>138.65</v>
       </c>
       <c r="G51">
         <v>70.40000000000001</v>
@@ -5457,37 +5457,37 @@
         <v>12</v>
       </c>
       <c r="M51">
-        <v>32.0397966</v>
+        <v>32.69367</v>
       </c>
       <c r="N51">
-        <v>-20.0397966</v>
+        <v>-20.69367</v>
       </c>
       <c r="O51">
-        <v>-6.813530844000002</v>
+        <v>-7.035847800000002</v>
       </c>
       <c r="P51">
-        <v>-13.226265756</v>
+        <v>-13.6578222</v>
       </c>
       <c r="Q51">
-        <v>28.173734244</v>
+        <v>27.7421778</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.151316870725527</v>
+        <v>0.1534272081400376</v>
       </c>
       <c r="T51">
-        <v>1.375238549913615</v>
+        <v>1.402743320911887</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1273416323747823</v>
+        <v>0.1247947997272867</v>
       </c>
       <c r="W51">
-        <v>0.2057728430860264</v>
+        <v>0.2063733862243058</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3745342128670067</v>
+        <v>0.3670435286096666</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1799002971821717</v>
+        <v>0.1818002971821717</v>
       </c>
       <c r="C52">
-        <v>62.22975856492835</v>
+        <v>58.36196829529428</v>
       </c>
       <c r="D52">
-        <v>130.4797585649283</v>
+        <v>129.3849682952943</v>
       </c>
       <c r="E52">
-        <v>-21.34999999999999</v>
+        <v>-18.577</v>
       </c>
       <c r="F52">
-        <v>138.65</v>
+        <v>141.423</v>
       </c>
       <c r="G52">
         <v>70.40000000000001</v>
@@ -5539,37 +5539,37 @@
         <v>12</v>
       </c>
       <c r="M52">
-        <v>32.69367</v>
+        <v>33.3475434</v>
       </c>
       <c r="N52">
-        <v>-20.69367</v>
+        <v>-21.3475434</v>
       </c>
       <c r="O52">
-        <v>-7.035847800000002</v>
+        <v>-7.258164756</v>
       </c>
       <c r="P52">
-        <v>-13.6578222</v>
+        <v>-14.089378644</v>
       </c>
       <c r="Q52">
-        <v>27.7421778</v>
+        <v>27.310621356</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1534272081400376</v>
+        <v>0.1556236817755486</v>
       </c>
       <c r="T52">
-        <v>1.402743320911887</v>
+        <v>1.431370735624375</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1247947997272867</v>
+        <v>0.1223478428698889</v>
       </c>
       <c r="W52">
-        <v>0.2063733862243058</v>
+        <v>0.2069503786512802</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3670435286096666</v>
+        <v>0.3598465966761438</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1818002971821717</v>
+        <v>0.1837002971821717</v>
       </c>
       <c r="C53">
-        <v>58.36196829529428</v>
+        <v>54.5123968338583</v>
       </c>
       <c r="D53">
-        <v>129.3849682952943</v>
+        <v>128.3083968338583</v>
       </c>
       <c r="E53">
-        <v>-18.577</v>
+        <v>-15.804</v>
       </c>
       <c r="F53">
-        <v>141.423</v>
+        <v>144.196</v>
       </c>
       <c r="G53">
         <v>70.40000000000001</v>
@@ -5621,37 +5621,37 @@
         <v>12</v>
       </c>
       <c r="M53">
-        <v>33.3475434</v>
+        <v>34.0014168</v>
       </c>
       <c r="N53">
-        <v>-21.3475434</v>
+        <v>-22.0014168</v>
       </c>
       <c r="O53">
-        <v>-7.258164756</v>
+        <v>-7.480481712000001</v>
       </c>
       <c r="P53">
-        <v>-14.089378644</v>
+        <v>-14.520935088</v>
       </c>
       <c r="Q53">
-        <v>27.310621356</v>
+        <v>26.879064912</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1556236817755486</v>
+        <v>0.1579116751458725</v>
       </c>
       <c r="T53">
-        <v>1.431370735624375</v>
+        <v>1.461190959283216</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1223478428698889</v>
+        <v>0.1199949997377757</v>
       </c>
       <c r="W53">
-        <v>0.2069503786512802</v>
+        <v>0.2075051790618325</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3598465966761438</v>
+        <v>0.3529264698169872</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1837002971821717</v>
+        <v>0.1856002971821717</v>
       </c>
       <c r="C54">
-        <v>54.5123968338583</v>
+        <v>50.68059315461684</v>
       </c>
       <c r="D54">
-        <v>128.3083968338583</v>
+        <v>127.2495931546168</v>
       </c>
       <c r="E54">
-        <v>-15.804</v>
+        <v>-13.03099999999998</v>
       </c>
       <c r="F54">
-        <v>144.196</v>
+        <v>146.969</v>
       </c>
       <c r="G54">
         <v>70.40000000000001</v>
@@ -5703,37 +5703,37 @@
         <v>12</v>
       </c>
       <c r="M54">
-        <v>34.0014168</v>
+        <v>34.65529020000001</v>
       </c>
       <c r="N54">
-        <v>-22.0014168</v>
+        <v>-22.65529020000001</v>
       </c>
       <c r="O54">
-        <v>-7.480481712000001</v>
+        <v>-7.702798668000004</v>
       </c>
       <c r="P54">
-        <v>-14.520935088</v>
+        <v>-14.95249153200001</v>
       </c>
       <c r="Q54">
-        <v>26.879064912</v>
+        <v>26.44750846799999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1579116751458725</v>
+        <v>0.1602970299362102</v>
       </c>
       <c r="T54">
-        <v>1.461190959283216</v>
+        <v>1.492280128629667</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1199949997377757</v>
+        <v>0.1177309431389497</v>
       </c>
       <c r="W54">
-        <v>0.2075051790618325</v>
+        <v>0.2080390436078357</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3529264698169872</v>
+        <v>0.3462674798204401</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1856002971821717</v>
+        <v>0.1875002971821717</v>
       </c>
       <c r="C55">
-        <v>50.68059315461684</v>
+        <v>46.86612099722527</v>
       </c>
       <c r="D55">
-        <v>127.2495931546168</v>
+        <v>126.2081209972253</v>
       </c>
       <c r="E55">
-        <v>-13.03099999999998</v>
+        <v>-10.25799999999998</v>
       </c>
       <c r="F55">
-        <v>146.969</v>
+        <v>149.742</v>
       </c>
       <c r="G55">
         <v>70.40000000000001</v>
@@ -5785,37 +5785,37 @@
         <v>12</v>
       </c>
       <c r="M55">
-        <v>34.65529020000001</v>
+        <v>35.30916360000001</v>
       </c>
       <c r="N55">
-        <v>-22.65529020000001</v>
+        <v>-23.30916360000001</v>
       </c>
       <c r="O55">
-        <v>-7.702798668000004</v>
+        <v>-7.925115624000003</v>
       </c>
       <c r="P55">
-        <v>-14.95249153200001</v>
+        <v>-15.384047976</v>
       </c>
       <c r="Q55">
-        <v>26.44750846799999</v>
+        <v>26.015952024</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1602970299362102</v>
+        <v>0.1627860958043887</v>
       </c>
       <c r="T55">
-        <v>1.492280128629667</v>
+        <v>1.524721000991182</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1177309431389497</v>
+        <v>0.1155507404882284</v>
       </c>
       <c r="W55">
-        <v>0.2080390436078357</v>
+        <v>0.2085531353928758</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3462674798204401</v>
+        <v>0.3398551190830246</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1875002971821717</v>
+        <v>0.1894002971821717</v>
       </c>
       <c r="C56">
-        <v>46.86612099722527</v>
+        <v>43.06855826765675</v>
       </c>
       <c r="D56">
-        <v>126.2081209972253</v>
+        <v>125.1835582676568</v>
       </c>
       <c r="E56">
-        <v>-10.25799999999998</v>
+        <v>-7.484999999999985</v>
       </c>
       <c r="F56">
-        <v>149.742</v>
+        <v>152.515</v>
       </c>
       <c r="G56">
         <v>70.40000000000001</v>
@@ -5867,37 +5867,37 @@
         <v>12</v>
       </c>
       <c r="M56">
-        <v>35.30916360000001</v>
+        <v>35.96303700000001</v>
       </c>
       <c r="N56">
-        <v>-23.30916360000001</v>
+        <v>-23.96303700000001</v>
       </c>
       <c r="O56">
-        <v>-7.925115624000003</v>
+        <v>-8.147432580000004</v>
       </c>
       <c r="P56">
-        <v>-15.384047976</v>
+        <v>-15.81560442</v>
       </c>
       <c r="Q56">
-        <v>26.015952024</v>
+        <v>25.58439558</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1627860958043887</v>
+        <v>0.165385786822264</v>
       </c>
       <c r="T56">
-        <v>1.524721000991182</v>
+        <v>1.558603689902097</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1155507404882284</v>
+        <v>0.113449817933897</v>
       </c>
       <c r="W56">
-        <v>0.2085531353928758</v>
+        <v>0.2090485329311871</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3398551190830246</v>
+        <v>0.3336759350996968</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1894002971821717</v>
+        <v>0.1913002971821717</v>
       </c>
       <c r="C57">
-        <v>43.06855826765675</v>
+        <v>39.28749646781915</v>
       </c>
       <c r="D57">
-        <v>125.1835582676568</v>
+        <v>124.1754964678191</v>
       </c>
       <c r="E57">
-        <v>-7.484999999999985</v>
+        <v>-4.711999999999989</v>
       </c>
       <c r="F57">
-        <v>152.515</v>
+        <v>155.288</v>
       </c>
       <c r="G57">
         <v>70.40000000000001</v>
@@ -5949,37 +5949,37 @@
         <v>12</v>
       </c>
       <c r="M57">
-        <v>35.96303700000001</v>
+        <v>36.6169104</v>
       </c>
       <c r="N57">
-        <v>-23.96303700000001</v>
+        <v>-24.6169104</v>
       </c>
       <c r="O57">
-        <v>-8.147432580000004</v>
+        <v>-8.369749536</v>
       </c>
       <c r="P57">
-        <v>-15.81560442</v>
+        <v>-16.247160864</v>
       </c>
       <c r="Q57">
-        <v>25.58439558</v>
+        <v>25.152839136</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.165385786822264</v>
+        <v>0.1681036456136791</v>
       </c>
       <c r="T57">
-        <v>1.558603689902097</v>
+        <v>1.594026501036236</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.113449817933897</v>
+        <v>0.1114239283279345</v>
       </c>
       <c r="W57">
-        <v>0.2090485329311871</v>
+        <v>0.209526237700273</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3336759350996968</v>
+        <v>0.3277174362586309</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1913002971821717</v>
+        <v>0.1932002971821717</v>
       </c>
       <c r="C58">
-        <v>39.28749646781915</v>
+        <v>35.52254015250969</v>
       </c>
       <c r="D58">
-        <v>124.1754964678191</v>
+        <v>123.1835401525097</v>
       </c>
       <c r="E58">
-        <v>-4.711999999999989</v>
+        <v>-1.938999999999965</v>
       </c>
       <c r="F58">
-        <v>155.288</v>
+        <v>158.061</v>
       </c>
       <c r="G58">
         <v>70.40000000000001</v>
@@ -6031,37 +6031,37 @@
         <v>12</v>
       </c>
       <c r="M58">
-        <v>36.6169104</v>
+        <v>37.27078380000001</v>
       </c>
       <c r="N58">
-        <v>-24.6169104</v>
+        <v>-25.27078380000001</v>
       </c>
       <c r="O58">
-        <v>-8.369749536</v>
+        <v>-8.592066492000004</v>
       </c>
       <c r="P58">
-        <v>-16.247160864</v>
+        <v>-16.67871730800001</v>
       </c>
       <c r="Q58">
-        <v>25.152839136</v>
+        <v>24.72128269199999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1681036456136791</v>
+        <v>0.1709479164419042</v>
       </c>
       <c r="T58">
-        <v>1.594026501036236</v>
+        <v>1.631096884781265</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1114239283279345</v>
+        <v>0.1094691225677953</v>
       </c>
       <c r="W58">
-        <v>0.209526237700273</v>
+        <v>0.2099871808985139</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3277174362586309</v>
+        <v>0.3219680075523391</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1932002971821717</v>
+        <v>0.1951002971821717</v>
       </c>
       <c r="C59">
-        <v>35.52254015250969</v>
+        <v>31.7733064121924</v>
       </c>
       <c r="D59">
-        <v>123.1835401525097</v>
+        <v>122.2073064121924</v>
       </c>
       <c r="E59">
-        <v>-1.938999999999965</v>
+        <v>0.8340000000000316</v>
       </c>
       <c r="F59">
-        <v>158.061</v>
+        <v>160.834</v>
       </c>
       <c r="G59">
         <v>70.40000000000001</v>
@@ -6113,37 +6113,37 @@
         <v>12</v>
       </c>
       <c r="M59">
-        <v>37.27078380000001</v>
+        <v>37.92465720000001</v>
       </c>
       <c r="N59">
-        <v>-25.27078380000001</v>
+        <v>-25.92465720000001</v>
       </c>
       <c r="O59">
-        <v>-8.592066492000004</v>
+        <v>-8.814383448000003</v>
       </c>
       <c r="P59">
-        <v>-16.67871730800001</v>
+        <v>-17.110273752</v>
       </c>
       <c r="Q59">
-        <v>24.72128269199999</v>
+        <v>24.28972624799999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1709479164419042</v>
+        <v>0.17392762873814</v>
       </c>
       <c r="T59">
-        <v>1.631096884781265</v>
+        <v>1.669932524895104</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1094691225677953</v>
+        <v>0.1075817239028333</v>
       </c>
       <c r="W59">
-        <v>0.2099871808985139</v>
+        <v>0.2104322295037119</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3219680075523391</v>
+        <v>0.3164168350083333</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1951002971821717</v>
+        <v>0.1970002971821717</v>
       </c>
       <c r="C60">
-        <v>31.77330641219243</v>
+        <v>28.03942438017575</v>
       </c>
       <c r="D60">
-        <v>122.2073064121924</v>
+        <v>121.2464243801757</v>
       </c>
       <c r="E60">
-        <v>0.8340000000000032</v>
+        <v>3.606999999999999</v>
       </c>
       <c r="F60">
-        <v>160.834</v>
+        <v>163.607</v>
       </c>
       <c r="G60">
         <v>70.40000000000001</v>
@@ -6195,37 +6195,37 @@
         <v>12</v>
       </c>
       <c r="M60">
-        <v>37.92465720000001</v>
+        <v>38.5785306</v>
       </c>
       <c r="N60">
-        <v>-25.92465720000001</v>
+        <v>-26.5785306</v>
       </c>
       <c r="O60">
-        <v>-8.814383448000003</v>
+        <v>-9.036700404000001</v>
       </c>
       <c r="P60">
-        <v>-17.110273752</v>
+        <v>-17.541830196</v>
       </c>
       <c r="Q60">
-        <v>24.28972624799999</v>
+        <v>23.858169804</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.17392762873814</v>
+        <v>0.1770526928537044</v>
       </c>
       <c r="T60">
-        <v>1.669932524895104</v>
+        <v>1.710662586477911</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1075817239028333</v>
+        <v>0.1057583048536328</v>
       </c>
       <c r="W60">
-        <v>0.2104322295037119</v>
+        <v>0.2108621917155134</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3164168350083333</v>
+        <v>0.3110538378048022</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1970002971821717</v>
+        <v>0.1989002971821717</v>
       </c>
       <c r="C61">
-        <v>28.03942438017575</v>
+        <v>24.32053476285827</v>
       </c>
       <c r="D61">
-        <v>121.2464243801757</v>
+        <v>120.3005347628583</v>
       </c>
       <c r="E61">
-        <v>3.606999999999999</v>
+        <v>6.379999999999995</v>
       </c>
       <c r="F61">
-        <v>163.607</v>
+        <v>166.38</v>
       </c>
       <c r="G61">
         <v>70.40000000000001</v>
@@ -6277,37 +6277,37 @@
         <v>12</v>
       </c>
       <c r="M61">
-        <v>38.5785306</v>
+        <v>39.232404</v>
       </c>
       <c r="N61">
-        <v>-26.5785306</v>
+        <v>-27.232404</v>
       </c>
       <c r="O61">
-        <v>-9.036700404000001</v>
+        <v>-9.259017360000001</v>
       </c>
       <c r="P61">
-        <v>-17.541830196</v>
+        <v>-17.97338664</v>
       </c>
       <c r="Q61">
-        <v>23.858169804</v>
+        <v>23.42661336</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1770526928537044</v>
+        <v>0.180334010175047</v>
       </c>
       <c r="T61">
-        <v>1.710662586477911</v>
+        <v>1.753429151139859</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1057583048536328</v>
+        <v>0.1039956664394055</v>
       </c>
       <c r="W61">
-        <v>0.2108621917155134</v>
+        <v>0.2112778218535882</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3110538378048022</v>
+        <v>0.3058696071747222</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1989002971821717</v>
+        <v>0.2008002971821717</v>
       </c>
       <c r="C62">
-        <v>24.32053476285827</v>
+        <v>20.61628939179295</v>
       </c>
       <c r="D62">
-        <v>120.3005347628583</v>
+        <v>119.3692893917929</v>
       </c>
       <c r="E62">
-        <v>6.379999999999995</v>
+        <v>9.152999999999992</v>
       </c>
       <c r="F62">
-        <v>166.38</v>
+        <v>169.153</v>
       </c>
       <c r="G62">
         <v>70.40000000000001</v>
@@ -6359,37 +6359,37 @@
         <v>12</v>
       </c>
       <c r="M62">
-        <v>39.232404</v>
+        <v>39.8862774</v>
       </c>
       <c r="N62">
-        <v>-27.232404</v>
+        <v>-27.8862774</v>
       </c>
       <c r="O62">
-        <v>-9.259017360000001</v>
+        <v>-9.481334316</v>
       </c>
       <c r="P62">
-        <v>-17.97338664</v>
+        <v>-18.404943084</v>
       </c>
       <c r="Q62">
-        <v>23.42661336</v>
+        <v>22.995056916</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.180334010175047</v>
+        <v>0.1837836001795354</v>
       </c>
       <c r="T62">
-        <v>1.753429151139859</v>
+        <v>1.798388872963958</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1039956664394055</v>
+        <v>0.1022908194485956</v>
       </c>
       <c r="W62">
-        <v>0.2112778218535882</v>
+        <v>0.2116798247740212</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3058696071747222</v>
+        <v>0.3008553513193989</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2008002971821717</v>
+        <v>0.2027002971821717</v>
       </c>
       <c r="C63">
-        <v>20.61628939179295</v>
+        <v>16.92635079639601</v>
       </c>
       <c r="D63">
-        <v>119.3692893917929</v>
+        <v>118.452350796396</v>
       </c>
       <c r="E63">
-        <v>9.152999999999992</v>
+        <v>11.92600000000002</v>
       </c>
       <c r="F63">
-        <v>169.153</v>
+        <v>171.926</v>
       </c>
       <c r="G63">
         <v>70.40000000000001</v>
@@ -6441,37 +6441,37 @@
         <v>12</v>
       </c>
       <c r="M63">
-        <v>39.8862774</v>
+        <v>40.54015080000001</v>
       </c>
       <c r="N63">
-        <v>-27.8862774</v>
+        <v>-28.54015080000001</v>
       </c>
       <c r="O63">
-        <v>-9.481334316</v>
+        <v>-9.703651272000004</v>
       </c>
       <c r="P63">
-        <v>-18.404943084</v>
+        <v>-18.836499528</v>
       </c>
       <c r="Q63">
-        <v>22.995056916</v>
+        <v>22.56350047199999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1837836001795354</v>
+        <v>0.187414747552681</v>
       </c>
       <c r="T63">
-        <v>1.798388872963958</v>
+        <v>1.845714895936694</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1022908194485956</v>
+        <v>0.1006409675220054</v>
       </c>
       <c r="W63">
-        <v>0.2116798247740212</v>
+        <v>0.2120688598583111</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3008553513193989</v>
+        <v>0.2960028456529569</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2027002971821717</v>
+        <v>0.2046002971821717</v>
       </c>
       <c r="C64">
-        <v>16.92635079639601</v>
+        <v>13.25039179619961</v>
       </c>
       <c r="D64">
-        <v>118.452350796396</v>
+        <v>117.5493917961996</v>
       </c>
       <c r="E64">
-        <v>11.92600000000002</v>
+        <v>14.69900000000001</v>
       </c>
       <c r="F64">
-        <v>171.926</v>
+        <v>174.699</v>
       </c>
       <c r="G64">
         <v>70.40000000000001</v>
@@ -6523,37 +6523,37 @@
         <v>12</v>
       </c>
       <c r="M64">
-        <v>40.54015080000001</v>
+        <v>41.1940242</v>
       </c>
       <c r="N64">
-        <v>-28.54015080000001</v>
+        <v>-29.1940242</v>
       </c>
       <c r="O64">
-        <v>-9.703651272000004</v>
+        <v>-9.925968228</v>
       </c>
       <c r="P64">
-        <v>-18.836499528</v>
+        <v>-19.268055972</v>
       </c>
       <c r="Q64">
-        <v>22.56350047199999</v>
+        <v>22.131944028</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.187414747552681</v>
+        <v>0.191242173162213</v>
       </c>
       <c r="T64">
-        <v>1.845714895936694</v>
+        <v>1.895599082313361</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1006409675220054</v>
+        <v>0.09904349184705291</v>
       </c>
       <c r="W64">
-        <v>0.2120688598583111</v>
+        <v>0.212445544622465</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2960028456529569</v>
+        <v>0.2913043877854498</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2046002971821717</v>
+        <v>0.2065002971821717</v>
       </c>
       <c r="C65">
-        <v>13.25039179619961</v>
+        <v>9.588095111612375</v>
       </c>
       <c r="D65">
-        <v>117.5493917961996</v>
+        <v>116.6600951116124</v>
       </c>
       <c r="E65">
-        <v>14.69900000000001</v>
+        <v>17.47200000000001</v>
       </c>
       <c r="F65">
-        <v>174.699</v>
+        <v>177.472</v>
       </c>
       <c r="G65">
         <v>70.40000000000001</v>
@@ -6605,37 +6605,37 @@
         <v>12</v>
       </c>
       <c r="M65">
-        <v>41.1940242</v>
+        <v>41.8478976</v>
       </c>
       <c r="N65">
-        <v>-29.1940242</v>
+        <v>-29.8478976</v>
       </c>
       <c r="O65">
-        <v>-9.925968228</v>
+        <v>-10.148285184</v>
       </c>
       <c r="P65">
-        <v>-19.268055972</v>
+        <v>-19.699612416</v>
       </c>
       <c r="Q65">
-        <v>22.131944028</v>
+        <v>21.700387584</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.191242173162213</v>
+        <v>0.19528223352783</v>
       </c>
       <c r="T65">
-        <v>1.895599082313361</v>
+        <v>1.948254612377621</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09904349184705291</v>
+        <v>0.0974959372869427</v>
       </c>
       <c r="W65">
-        <v>0.212445544622465</v>
+        <v>0.2128104579877389</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2913043877854498</v>
+        <v>0.2867527567263021</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2065002971821717</v>
+        <v>0.2084002971821717</v>
       </c>
       <c r="C66">
-        <v>9.588095111612375</v>
+        <v>5.939152992216009</v>
       </c>
       <c r="D66">
-        <v>116.6600951116124</v>
+        <v>115.784152992216</v>
       </c>
       <c r="E66">
-        <v>17.47200000000001</v>
+        <v>20.245</v>
       </c>
       <c r="F66">
-        <v>177.472</v>
+        <v>180.245</v>
       </c>
       <c r="G66">
         <v>70.40000000000001</v>
@@ -6687,37 +6687,37 @@
         <v>12</v>
       </c>
       <c r="M66">
-        <v>41.8478976</v>
+        <v>42.50177100000001</v>
       </c>
       <c r="N66">
-        <v>-29.8478976</v>
+        <v>-30.50177100000001</v>
       </c>
       <c r="O66">
-        <v>-10.148285184</v>
+        <v>-10.37060214</v>
       </c>
       <c r="P66">
-        <v>-19.699612416</v>
+        <v>-20.13116886</v>
       </c>
       <c r="Q66">
-        <v>21.700387584</v>
+        <v>21.26883114</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.19528223352783</v>
+        <v>0.199553154485768</v>
       </c>
       <c r="T66">
-        <v>1.948254612377621</v>
+        <v>2.003919029874125</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0974959372869427</v>
+        <v>0.0959959997902205</v>
       </c>
       <c r="W66">
-        <v>0.2128104579877389</v>
+        <v>0.213164143249466</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2867527567263021</v>
+        <v>0.2823411758535896</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2084002971821717</v>
+        <v>0.2103002971821717</v>
       </c>
       <c r="C67">
-        <v>5.939152992216009</v>
+        <v>2.303266861682403</v>
       </c>
       <c r="D67">
-        <v>115.784152992216</v>
+        <v>114.9212668616824</v>
       </c>
       <c r="E67">
-        <v>20.245</v>
+        <v>23.01800000000003</v>
       </c>
       <c r="F67">
-        <v>180.245</v>
+        <v>183.018</v>
       </c>
       <c r="G67">
         <v>70.40000000000001</v>
@@ -6769,37 +6769,37 @@
         <v>12</v>
       </c>
       <c r="M67">
-        <v>42.50177100000001</v>
+        <v>43.15564440000001</v>
       </c>
       <c r="N67">
-        <v>-30.50177100000001</v>
+        <v>-31.15564440000001</v>
       </c>
       <c r="O67">
-        <v>-10.37060214</v>
+        <v>-10.592919096</v>
       </c>
       <c r="P67">
-        <v>-20.13116886</v>
+        <v>-20.562725304</v>
       </c>
       <c r="Q67">
-        <v>21.26883114</v>
+        <v>20.83727469599999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.199553154485768</v>
+        <v>0.2040753060882906</v>
       </c>
       <c r="T67">
-        <v>2.003919029874125</v>
+        <v>2.062857824870423</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0959959997902205</v>
+        <v>0.09454151494491411</v>
       </c>
       <c r="W67">
-        <v>0.213164143249466</v>
+        <v>0.2135071107759892</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2823411758535896</v>
+        <v>0.2780632792497474</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2103002971821717</v>
+        <v>0.2122002971821717</v>
       </c>
       <c r="C68">
-        <v>2.303266861682403</v>
+        <v>-1.319853021548766</v>
       </c>
       <c r="D68">
-        <v>114.9212668616824</v>
+        <v>114.0711469784513</v>
       </c>
       <c r="E68">
-        <v>23.01800000000003</v>
+        <v>25.79100000000003</v>
       </c>
       <c r="F68">
-        <v>183.018</v>
+        <v>185.791</v>
       </c>
       <c r="G68">
         <v>70.40000000000001</v>
@@ -6851,37 +6851,37 @@
         <v>12</v>
       </c>
       <c r="M68">
-        <v>43.15564440000001</v>
+        <v>43.80951780000001</v>
       </c>
       <c r="N68">
-        <v>-31.15564440000001</v>
+        <v>-31.80951780000001</v>
       </c>
       <c r="O68">
-        <v>-10.592919096</v>
+        <v>-10.815236052</v>
       </c>
       <c r="P68">
-        <v>-20.562725304</v>
+        <v>-20.99428174800001</v>
       </c>
       <c r="Q68">
-        <v>20.83727469599999</v>
+        <v>20.40571825199999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2040753060882906</v>
+        <v>0.2088715274849055</v>
       </c>
       <c r="T68">
-        <v>2.062857824870423</v>
+        <v>2.125368668048315</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09454151494491411</v>
+        <v>0.09313044755767659</v>
       </c>
       <c r="W68">
-        <v>0.2135071107759892</v>
+        <v>0.2138398404658998</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2780632792497474</v>
+        <v>0.27391308105199</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2122002971821717</v>
+        <v>0.2141002971821717</v>
       </c>
       <c r="C69">
-        <v>-1.319853021548766</v>
+        <v>-4.930487888642801</v>
       </c>
       <c r="D69">
-        <v>114.0711469784513</v>
+        <v>113.2335121113572</v>
       </c>
       <c r="E69">
-        <v>25.79100000000003</v>
+        <v>28.56400000000002</v>
       </c>
       <c r="F69">
-        <v>185.791</v>
+        <v>188.564</v>
       </c>
       <c r="G69">
         <v>70.40000000000001</v>
@@ -6933,37 +6933,37 @@
         <v>12</v>
       </c>
       <c r="M69">
-        <v>43.80951780000001</v>
+        <v>44.4633912</v>
       </c>
       <c r="N69">
-        <v>-31.80951780000001</v>
+        <v>-32.4633912</v>
       </c>
       <c r="O69">
-        <v>-10.815236052</v>
+        <v>-11.037553008</v>
       </c>
       <c r="P69">
-        <v>-20.99428174800001</v>
+        <v>-21.425838192</v>
       </c>
       <c r="Q69">
-        <v>20.40571825199999</v>
+        <v>19.974161808</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2088715274849055</v>
+        <v>0.2139675127188087</v>
       </c>
       <c r="T69">
-        <v>2.125368668048315</v>
+        <v>2.191786438924824</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09313044755767659</v>
+        <v>0.09176088215241665</v>
       </c>
       <c r="W69">
-        <v>0.2138398404658998</v>
+        <v>0.2141627839884602</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.27391308105199</v>
+        <v>0.2698849475071078</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2141002971821717</v>
+        <v>0.2160002971821717</v>
       </c>
       <c r="C70">
-        <v>-4.930487888642801</v>
+        <v>-8.528910770555143</v>
       </c>
       <c r="D70">
-        <v>113.2335121113572</v>
+        <v>112.4080892294449</v>
       </c>
       <c r="E70">
-        <v>28.56400000000002</v>
+        <v>31.33700000000002</v>
       </c>
       <c r="F70">
-        <v>188.564</v>
+        <v>191.337</v>
       </c>
       <c r="G70">
         <v>70.40000000000001</v>
@@ -7015,37 +7015,37 @@
         <v>12</v>
       </c>
       <c r="M70">
-        <v>44.4633912</v>
+        <v>45.11726460000001</v>
       </c>
       <c r="N70">
-        <v>-32.4633912</v>
+        <v>-33.11726460000001</v>
       </c>
       <c r="O70">
-        <v>-11.037553008</v>
+        <v>-11.259869964</v>
       </c>
       <c r="P70">
-        <v>-21.425838192</v>
+        <v>-21.857394636</v>
       </c>
       <c r="Q70">
-        <v>19.974161808</v>
+        <v>19.542605364</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2139675127188087</v>
+        <v>0.219392271193609</v>
       </c>
       <c r="T70">
-        <v>2.191786438924824</v>
+        <v>2.262489227277238</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09176088215241665</v>
+        <v>0.09043101429513525</v>
       </c>
       <c r="W70">
-        <v>0.2141627839884602</v>
+        <v>0.2144763668292071</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2698849475071078</v>
+        <v>0.2659735714562801</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2160002971821717</v>
+        <v>0.2179002971821717</v>
       </c>
       <c r="C71">
-        <v>-8.528910770555143</v>
+        <v>-12.11538679474825</v>
       </c>
       <c r="D71">
-        <v>112.4080892294449</v>
+        <v>111.5946132052518</v>
       </c>
       <c r="E71">
-        <v>31.33700000000002</v>
+        <v>34.11000000000001</v>
       </c>
       <c r="F71">
-        <v>191.337</v>
+        <v>194.11</v>
       </c>
       <c r="G71">
         <v>70.40000000000001</v>
@@ -7097,37 +7097,37 @@
         <v>12</v>
       </c>
       <c r="M71">
-        <v>45.11726460000001</v>
+        <v>45.77113800000001</v>
       </c>
       <c r="N71">
-        <v>-33.11726460000001</v>
+        <v>-33.77113800000001</v>
       </c>
       <c r="O71">
-        <v>-11.259869964</v>
+        <v>-11.48218692</v>
       </c>
       <c r="P71">
-        <v>-21.857394636</v>
+        <v>-22.28895108</v>
       </c>
       <c r="Q71">
-        <v>19.542605364</v>
+        <v>19.11104891999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.219392271193609</v>
+        <v>0.225178680233396</v>
       </c>
       <c r="T71">
-        <v>2.262489227277238</v>
+        <v>2.337905534853146</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09043101429513525</v>
+        <v>0.08913914266234761</v>
       </c>
       <c r="W71">
-        <v>0.2144763668292071</v>
+        <v>0.2147809901602185</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2659735714562801</v>
+        <v>0.2621739490069047</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2179002971821717</v>
+        <v>0.2198002971821717</v>
       </c>
       <c r="C72">
-        <v>-12.11538679474825</v>
+        <v>-15.69017346911738</v>
       </c>
       <c r="D72">
-        <v>111.5946132052518</v>
+        <v>110.7928265308826</v>
       </c>
       <c r="E72">
-        <v>34.11000000000001</v>
+        <v>36.88300000000004</v>
       </c>
       <c r="F72">
-        <v>194.11</v>
+        <v>196.883</v>
       </c>
       <c r="G72">
         <v>70.40000000000001</v>
@@ -7179,37 +7179,37 @@
         <v>12</v>
       </c>
       <c r="M72">
-        <v>45.77113800000001</v>
+        <v>46.42501140000001</v>
       </c>
       <c r="N72">
-        <v>-33.77113800000001</v>
+        <v>-34.42501140000001</v>
       </c>
       <c r="O72">
-        <v>-11.48218692</v>
+        <v>-11.704503876</v>
       </c>
       <c r="P72">
-        <v>-22.28895108</v>
+        <v>-22.72050752400001</v>
       </c>
       <c r="Q72">
-        <v>19.11104891999999</v>
+        <v>18.67949247599999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.225178680233396</v>
+        <v>0.2313641519655821</v>
       </c>
       <c r="T72">
-        <v>2.337905534853146</v>
+        <v>2.418522967089462</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08913914266234761</v>
+        <v>0.08788366177977933</v>
       </c>
       <c r="W72">
-        <v>0.2147809901602185</v>
+        <v>0.215077032552328</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2621739490069047</v>
+        <v>0.2584813581758215</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2198002971821717</v>
+        <v>0.2217002971821717</v>
       </c>
       <c r="C73">
-        <v>-15.69017346911735</v>
+        <v>-19.2535209537636</v>
       </c>
       <c r="D73">
-        <v>110.7928265308826</v>
+        <v>110.0024790462364</v>
       </c>
       <c r="E73">
-        <v>36.88300000000001</v>
+        <v>39.65600000000001</v>
       </c>
       <c r="F73">
-        <v>196.883</v>
+        <v>199.656</v>
       </c>
       <c r="G73">
         <v>70.40000000000001</v>
@@ -7261,37 +7261,37 @@
         <v>12</v>
       </c>
       <c r="M73">
-        <v>46.4250114</v>
+        <v>47.0788848</v>
       </c>
       <c r="N73">
-        <v>-34.4250114</v>
+        <v>-35.0788848</v>
       </c>
       <c r="O73">
-        <v>-11.704503876</v>
+        <v>-11.926820832</v>
       </c>
       <c r="P73">
-        <v>-22.720507524</v>
+        <v>-23.152063968</v>
       </c>
       <c r="Q73">
-        <v>18.679492476</v>
+        <v>18.247936032</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.231364151965582</v>
+        <v>0.23799144310721</v>
       </c>
       <c r="T73">
-        <v>2.418522967089461</v>
+        <v>2.504898787342656</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08788366177977934</v>
+        <v>0.08666305536617129</v>
       </c>
       <c r="W73">
-        <v>0.215077032552328</v>
+        <v>0.2153648515446568</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2584813581758215</v>
+        <v>0.2548913393122685</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2217002971821717</v>
+        <v>0.2236002971821717</v>
       </c>
       <c r="C74">
-        <v>-19.2535209537636</v>
+        <v>-22.80567232121743</v>
       </c>
       <c r="D74">
-        <v>110.0024790462364</v>
+        <v>109.2233276787826</v>
       </c>
       <c r="E74">
-        <v>39.65600000000001</v>
+        <v>42.429</v>
       </c>
       <c r="F74">
-        <v>199.656</v>
+        <v>202.429</v>
       </c>
       <c r="G74">
         <v>70.40000000000001</v>
@@ -7343,37 +7343,37 @@
         <v>12</v>
       </c>
       <c r="M74">
-        <v>47.0788848</v>
+        <v>47.7327582</v>
       </c>
       <c r="N74">
-        <v>-35.0788848</v>
+        <v>-35.7327582</v>
       </c>
       <c r="O74">
-        <v>-11.926820832</v>
+        <v>-12.149137788</v>
       </c>
       <c r="P74">
-        <v>-23.152063968</v>
+        <v>-23.583620412</v>
       </c>
       <c r="Q74">
-        <v>18.247936032</v>
+        <v>17.816379588</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.23799144310721</v>
+        <v>0.2451096447037732</v>
       </c>
       <c r="T74">
-        <v>2.504898787342656</v>
+        <v>2.597672816503494</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08666305536617129</v>
+        <v>0.08547589022416896</v>
       </c>
       <c r="W74">
-        <v>0.2153648515446568</v>
+        <v>0.215644785085141</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2548913393122685</v>
+        <v>0.2513996771299086</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2236002971821717</v>
+        <v>0.2255002971821717</v>
       </c>
       <c r="C75">
-        <v>-22.80567232121743</v>
+        <v>-26.34686380568098</v>
       </c>
       <c r="D75">
-        <v>109.2233276787826</v>
+        <v>108.455136194319</v>
       </c>
       <c r="E75">
-        <v>42.429</v>
+        <v>45.202</v>
       </c>
       <c r="F75">
-        <v>202.429</v>
+        <v>205.202</v>
       </c>
       <c r="G75">
         <v>70.40000000000001</v>
@@ -7425,37 +7425,37 @@
         <v>12</v>
       </c>
       <c r="M75">
-        <v>47.7327582</v>
+        <v>48.3866316</v>
       </c>
       <c r="N75">
-        <v>-35.7327582</v>
+        <v>-36.3866316</v>
       </c>
       <c r="O75">
-        <v>-12.149137788</v>
+        <v>-12.371454744</v>
       </c>
       <c r="P75">
-        <v>-23.583620412</v>
+        <v>-24.015176856</v>
       </c>
       <c r="Q75">
-        <v>17.816379588</v>
+        <v>17.384823144</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2451096447037732</v>
+        <v>0.2527754002693031</v>
       </c>
       <c r="T75">
-        <v>2.597672816503494</v>
+        <v>2.697583309445937</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08547589022416896</v>
+        <v>0.08432081062654505</v>
       </c>
       <c r="W75">
-        <v>0.215644785085141</v>
+        <v>0.2159171528542607</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2513996771299086</v>
+        <v>0.2480023841957207</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2255002971821717</v>
+        <v>0.2274002971821717</v>
       </c>
       <c r="C76">
-        <v>-26.34686380568098</v>
+        <v>-29.8773250418256</v>
       </c>
       <c r="D76">
-        <v>108.455136194319</v>
+        <v>107.6976749581744</v>
       </c>
       <c r="E76">
-        <v>45.202</v>
+        <v>47.97500000000002</v>
       </c>
       <c r="F76">
-        <v>205.202</v>
+        <v>207.975</v>
       </c>
       <c r="G76">
         <v>70.40000000000001</v>
@@ -7507,37 +7507,37 @@
         <v>12</v>
       </c>
       <c r="M76">
-        <v>48.3866316</v>
+        <v>49.04050500000001</v>
       </c>
       <c r="N76">
-        <v>-36.3866316</v>
+        <v>-37.04050500000001</v>
       </c>
       <c r="O76">
-        <v>-12.371454744</v>
+        <v>-12.5937717</v>
       </c>
       <c r="P76">
-        <v>-24.015176856</v>
+        <v>-24.44673330000001</v>
       </c>
       <c r="Q76">
-        <v>17.384823144</v>
+        <v>16.95326669999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2527754002693031</v>
+        <v>0.2610544162800752</v>
       </c>
       <c r="T76">
-        <v>2.697583309445937</v>
+        <v>2.805486641823775</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08432081062654505</v>
+        <v>0.08319653315152442</v>
       </c>
       <c r="W76">
-        <v>0.2159171528542607</v>
+        <v>0.2161822574828705</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2480023841957207</v>
+        <v>0.2446956857397777</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2274002971821717</v>
+        <v>0.2293002971821717</v>
       </c>
       <c r="C77">
-        <v>-29.8773250418256</v>
+        <v>-33.39727929365219</v>
       </c>
       <c r="D77">
-        <v>107.6976749581744</v>
+        <v>106.9507207063478</v>
       </c>
       <c r="E77">
-        <v>47.97500000000002</v>
+        <v>50.74800000000002</v>
       </c>
       <c r="F77">
-        <v>207.975</v>
+        <v>210.748</v>
       </c>
       <c r="G77">
         <v>70.40000000000001</v>
@@ -7589,37 +7589,37 @@
         <v>12</v>
       </c>
       <c r="M77">
-        <v>49.04050500000001</v>
+        <v>49.69437840000001</v>
       </c>
       <c r="N77">
-        <v>-37.04050500000001</v>
+        <v>-37.69437840000001</v>
       </c>
       <c r="O77">
-        <v>-12.5937717</v>
+        <v>-12.816088656</v>
       </c>
       <c r="P77">
-        <v>-24.44673330000001</v>
+        <v>-24.878289744</v>
       </c>
       <c r="Q77">
-        <v>16.95326669999999</v>
+        <v>16.521710256</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2610544162800752</v>
+        <v>0.270023350291745</v>
       </c>
       <c r="T77">
-        <v>2.805486641823775</v>
+        <v>2.922381918566432</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08319653315152442</v>
+        <v>0.08210184192584648</v>
       </c>
       <c r="W77">
-        <v>0.2161822574828705</v>
+        <v>0.2164403856738854</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2446956857397777</v>
+        <v>0.2414760056642543</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2293002971821717</v>
+        <v>0.2312002971821717</v>
       </c>
       <c r="C78">
-        <v>-33.39727929365219</v>
+        <v>-36.90694367389392</v>
       </c>
       <c r="D78">
-        <v>106.9507207063478</v>
+        <v>106.2140563261061</v>
       </c>
       <c r="E78">
-        <v>50.74800000000002</v>
+        <v>53.52100000000002</v>
       </c>
       <c r="F78">
-        <v>210.748</v>
+        <v>213.521</v>
       </c>
       <c r="G78">
         <v>70.40000000000001</v>
@@ -7671,37 +7671,37 @@
         <v>12</v>
       </c>
       <c r="M78">
-        <v>49.69437840000001</v>
+        <v>50.34825180000001</v>
       </c>
       <c r="N78">
-        <v>-37.69437840000001</v>
+        <v>-38.34825180000001</v>
       </c>
       <c r="O78">
-        <v>-12.816088656</v>
+        <v>-13.038405612</v>
       </c>
       <c r="P78">
-        <v>-24.878289744</v>
+        <v>-25.309846188</v>
       </c>
       <c r="Q78">
-        <v>16.521710256</v>
+        <v>16.090153812</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.270023350291745</v>
+        <v>0.2797721916087774</v>
       </c>
       <c r="T78">
-        <v>2.922381918566432</v>
+        <v>3.049442001982364</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08210184192584648</v>
+        <v>0.08103558423849783</v>
       </c>
       <c r="W78">
-        <v>0.2164403856738854</v>
+        <v>0.2166918092365622</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2414760056642543</v>
+        <v>0.2383399536426406</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2312002971821717</v>
+        <v>0.2331002971821717</v>
       </c>
       <c r="C79">
-        <v>-36.90694367389392</v>
+        <v>-40.4065293544127</v>
       </c>
       <c r="D79">
-        <v>106.2140563261061</v>
+        <v>105.4874706455873</v>
       </c>
       <c r="E79">
-        <v>53.52100000000002</v>
+        <v>56.29400000000001</v>
       </c>
       <c r="F79">
-        <v>213.521</v>
+        <v>216.294</v>
       </c>
       <c r="G79">
         <v>70.40000000000001</v>
@@ -7753,37 +7753,37 @@
         <v>12</v>
       </c>
       <c r="M79">
-        <v>50.34825180000001</v>
+        <v>51.0021252</v>
       </c>
       <c r="N79">
-        <v>-38.34825180000001</v>
+        <v>-39.0021252</v>
       </c>
       <c r="O79">
-        <v>-13.038405612</v>
+        <v>-13.260722568</v>
       </c>
       <c r="P79">
-        <v>-25.309846188</v>
+        <v>-25.741402632</v>
       </c>
       <c r="Q79">
-        <v>16.090153812</v>
+        <v>15.658597368</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2797721916087774</v>
+        <v>0.2904072912273581</v>
       </c>
       <c r="T79">
-        <v>3.049442001982364</v>
+        <v>3.188053002072472</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08103558423849783</v>
+        <v>0.07999666649185043</v>
       </c>
       <c r="W79">
-        <v>0.2166918092365622</v>
+        <v>0.2169367860412217</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2383399536426406</v>
+        <v>0.2352843132113248</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2331002971821717</v>
+        <v>0.2350002971821717</v>
       </c>
       <c r="C80">
-        <v>-40.4065293544127</v>
+        <v>-43.89624176801954</v>
       </c>
       <c r="D80">
-        <v>105.4874706455873</v>
+        <v>104.7707582319805</v>
       </c>
       <c r="E80">
-        <v>56.29400000000001</v>
+        <v>59.06700000000001</v>
       </c>
       <c r="F80">
-        <v>216.294</v>
+        <v>219.067</v>
       </c>
       <c r="G80">
         <v>70.40000000000001</v>
@@ -7835,37 +7835,37 @@
         <v>12</v>
       </c>
       <c r="M80">
-        <v>51.0021252</v>
+        <v>51.6559986</v>
       </c>
       <c r="N80">
-        <v>-39.0021252</v>
+        <v>-39.6559986</v>
       </c>
       <c r="O80">
-        <v>-13.260722568</v>
+        <v>-13.483039524</v>
       </c>
       <c r="P80">
-        <v>-25.741402632</v>
+        <v>-26.172959076</v>
       </c>
       <c r="Q80">
-        <v>15.658597368</v>
+        <v>15.227040924</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2904072912273581</v>
+        <v>0.30205525747628</v>
       </c>
       <c r="T80">
-        <v>3.188053002072472</v>
+        <v>3.339865049790208</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07999666649185043</v>
+        <v>0.07898405046030801</v>
       </c>
       <c r="W80">
-        <v>0.2169367860412217</v>
+        <v>0.2171755609014594</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2352843132113248</v>
+        <v>0.2323060307656117</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2350002971821717</v>
+        <v>0.2369002971821717</v>
       </c>
       <c r="C81">
-        <v>-43.89624176801954</v>
+        <v>-47.37628080212244</v>
       </c>
       <c r="D81">
-        <v>104.7707582319805</v>
+        <v>104.0637191978776</v>
       </c>
       <c r="E81">
-        <v>59.06700000000001</v>
+        <v>61.84000000000003</v>
       </c>
       <c r="F81">
-        <v>219.067</v>
+        <v>221.84</v>
       </c>
       <c r="G81">
         <v>70.40000000000001</v>
@@ -7917,37 +7917,37 @@
         <v>12</v>
       </c>
       <c r="M81">
-        <v>51.6559986</v>
+        <v>52.30987200000001</v>
       </c>
       <c r="N81">
-        <v>-39.6559986</v>
+        <v>-40.30987200000001</v>
       </c>
       <c r="O81">
-        <v>-13.483039524</v>
+        <v>-13.70535648000001</v>
       </c>
       <c r="P81">
-        <v>-26.172959076</v>
+        <v>-26.60451552000001</v>
       </c>
       <c r="Q81">
-        <v>15.227040924</v>
+        <v>14.79548447999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.30205525747628</v>
+        <v>0.314868020350094</v>
       </c>
       <c r="T81">
-        <v>3.339865049790208</v>
+        <v>3.506858302279719</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07898405046030801</v>
+        <v>0.07799674982955414</v>
       </c>
       <c r="W81">
-        <v>0.2171755609014594</v>
+        <v>0.2174083663901911</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2323060307656117</v>
+        <v>0.2294022053810416</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2369002971821717</v>
+        <v>0.2388002971821717</v>
       </c>
       <c r="C82">
-        <v>-47.37628080212244</v>
+        <v>-50.84684098458635</v>
       </c>
       <c r="D82">
-        <v>104.0637191978776</v>
+        <v>103.3661590154137</v>
       </c>
       <c r="E82">
-        <v>61.84000000000003</v>
+        <v>64.61300000000003</v>
       </c>
       <c r="F82">
-        <v>221.84</v>
+        <v>224.613</v>
       </c>
       <c r="G82">
         <v>70.40000000000001</v>
@@ -7999,37 +7999,37 @@
         <v>12</v>
       </c>
       <c r="M82">
-        <v>52.30987200000001</v>
+        <v>52.96374540000001</v>
       </c>
       <c r="N82">
-        <v>-40.30987200000001</v>
+        <v>-40.96374540000001</v>
       </c>
       <c r="O82">
-        <v>-13.70535648000001</v>
+        <v>-13.927673436</v>
       </c>
       <c r="P82">
-        <v>-26.60451552000001</v>
+        <v>-27.036071964</v>
       </c>
       <c r="Q82">
-        <v>14.79548447999999</v>
+        <v>14.36392803599999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.314868020350094</v>
+        <v>0.3290294951053622</v>
       </c>
       <c r="T82">
-        <v>3.506858302279719</v>
+        <v>3.691429791873389</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07799674982955414</v>
+        <v>0.07703382699215226</v>
       </c>
       <c r="W82">
-        <v>0.2174083663901911</v>
+        <v>0.2176354235952505</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2294022053810416</v>
+        <v>0.2265700793886831</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2388002971821717</v>
+        <v>0.2407002971821717</v>
       </c>
       <c r="C83">
-        <v>-50.84684098458635</v>
+        <v>-54.30811166216762</v>
       </c>
       <c r="D83">
-        <v>103.3661590154137</v>
+        <v>102.6778883378324</v>
       </c>
       <c r="E83">
-        <v>64.61300000000003</v>
+        <v>67.38600000000002</v>
       </c>
       <c r="F83">
-        <v>224.613</v>
+        <v>227.386</v>
       </c>
       <c r="G83">
         <v>70.40000000000001</v>
@@ -8081,37 +8081,37 @@
         <v>12</v>
       </c>
       <c r="M83">
-        <v>52.96374540000001</v>
+        <v>53.61761880000001</v>
       </c>
       <c r="N83">
-        <v>-40.96374540000001</v>
+        <v>-41.61761880000001</v>
       </c>
       <c r="O83">
-        <v>-13.927673436</v>
+        <v>-14.149990392</v>
       </c>
       <c r="P83">
-        <v>-27.036071964</v>
+        <v>-27.467628408</v>
       </c>
       <c r="Q83">
-        <v>14.36392803599999</v>
+        <v>13.932371592</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3290294951053622</v>
+        <v>0.3447644670556601</v>
       </c>
       <c r="T83">
-        <v>3.691429791873389</v>
+        <v>3.896509224755244</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07703382699215226</v>
+        <v>0.0760943900776138</v>
       </c>
       <c r="W83">
-        <v>0.2176354235952505</v>
+        <v>0.2178569428196987</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2265700793886831</v>
+        <v>0.2238070296400406</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2407002971821717</v>
+        <v>0.2426002971821717</v>
       </c>
       <c r="C84">
-        <v>-54.30811166216762</v>
+        <v>-57.76027717186673</v>
       </c>
       <c r="D84">
-        <v>102.6778883378324</v>
+        <v>101.9987228281333</v>
       </c>
       <c r="E84">
-        <v>67.38600000000002</v>
+        <v>70.15900000000002</v>
       </c>
       <c r="F84">
-        <v>227.386</v>
+        <v>230.159</v>
       </c>
       <c r="G84">
         <v>70.40000000000001</v>
@@ -8163,37 +8163,37 @@
         <v>12</v>
       </c>
       <c r="M84">
-        <v>53.61761880000001</v>
+        <v>54.2714922</v>
       </c>
       <c r="N84">
-        <v>-41.61761880000001</v>
+        <v>-42.2714922</v>
       </c>
       <c r="O84">
-        <v>-14.149990392</v>
+        <v>-14.372307348</v>
       </c>
       <c r="P84">
-        <v>-27.467628408</v>
+        <v>-27.899184852</v>
       </c>
       <c r="Q84">
-        <v>13.932371592</v>
+        <v>13.500815148</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3447644670556601</v>
+        <v>0.3623506121765813</v>
       </c>
       <c r="T84">
-        <v>3.896509224755244</v>
+        <v>4.125715649740846</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0760943900776138</v>
+        <v>0.07517759019716064</v>
       </c>
       <c r="W84">
-        <v>0.2178569428196987</v>
+        <v>0.2180731242315095</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2238070296400406</v>
+        <v>0.2211105594034136</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2426002971821717</v>
+        <v>0.2445002971821718</v>
       </c>
       <c r="C85">
-        <v>-57.76027717186673</v>
+        <v>-61.20351700552547</v>
       </c>
       <c r="D85">
-        <v>101.9987228281333</v>
+        <v>101.3284829944746</v>
       </c>
       <c r="E85">
-        <v>70.15900000000002</v>
+        <v>72.93200000000004</v>
       </c>
       <c r="F85">
-        <v>230.159</v>
+        <v>232.932</v>
       </c>
       <c r="G85">
         <v>70.40000000000001</v>
@@ -8245,37 +8245,37 @@
         <v>12</v>
       </c>
       <c r="M85">
-        <v>54.2714922</v>
+        <v>54.92536560000001</v>
       </c>
       <c r="N85">
-        <v>-42.2714922</v>
+        <v>-42.92536560000001</v>
       </c>
       <c r="O85">
-        <v>-14.372307348</v>
+        <v>-14.59462430400001</v>
       </c>
       <c r="P85">
-        <v>-27.899184852</v>
+        <v>-28.33074129600001</v>
       </c>
       <c r="Q85">
-        <v>13.500815148</v>
+        <v>13.06925870399999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3623506121765813</v>
+        <v>0.3821350254376177</v>
       </c>
       <c r="T85">
-        <v>4.125715649740846</v>
+        <v>4.383572877849651</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07517759019716064</v>
+        <v>0.07428261888528967</v>
       </c>
       <c r="W85">
-        <v>0.2180731242315095</v>
+        <v>0.2182841584668487</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2211105594034136</v>
+        <v>0.2184782908390872</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2445002971821717</v>
+        <v>0.2464002971821717</v>
       </c>
       <c r="C86">
-        <v>-61.20351700552541</v>
+        <v>-64.63800596797682</v>
       </c>
       <c r="D86">
-        <v>101.3284829944746</v>
+        <v>100.6669940320232</v>
       </c>
       <c r="E86">
-        <v>72.93199999999999</v>
+        <v>75.70500000000001</v>
       </c>
       <c r="F86">
-        <v>232.932</v>
+        <v>235.705</v>
       </c>
       <c r="G86">
         <v>70.40000000000001</v>
@@ -8327,37 +8327,37 @@
         <v>12</v>
       </c>
       <c r="M86">
-        <v>54.9253656</v>
+        <v>55.57923900000001</v>
       </c>
       <c r="N86">
-        <v>-42.9253656</v>
+        <v>-43.57923900000001</v>
       </c>
       <c r="O86">
-        <v>-14.594624304</v>
+        <v>-14.81694126</v>
       </c>
       <c r="P86">
-        <v>-28.330741296</v>
+        <v>-28.76229774</v>
       </c>
       <c r="Q86">
-        <v>13.069258704</v>
+        <v>12.63770225999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3821350254376174</v>
+        <v>0.404557360466792</v>
       </c>
       <c r="T86">
-        <v>4.383572877849647</v>
+        <v>4.675811069706291</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07428261888528968</v>
+        <v>0.07340870572193332</v>
       </c>
       <c r="W86">
-        <v>0.2182841584668487</v>
+        <v>0.2184902271907681</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2184782908390873</v>
+        <v>0.2159079580056862</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2464002971821717</v>
+        <v>0.2483002971821717</v>
       </c>
       <c r="C87">
-        <v>-64.63800596797682</v>
+        <v>-68.06391432904064</v>
       </c>
       <c r="D87">
-        <v>100.6669940320232</v>
+        <v>100.0140856709594</v>
       </c>
       <c r="E87">
-        <v>75.70500000000001</v>
+        <v>78.47800000000001</v>
       </c>
       <c r="F87">
-        <v>235.705</v>
+        <v>238.478</v>
       </c>
       <c r="G87">
         <v>70.40000000000001</v>
@@ -8409,37 +8409,37 @@
         <v>12</v>
       </c>
       <c r="M87">
-        <v>55.57923900000001</v>
+        <v>56.2331124</v>
       </c>
       <c r="N87">
-        <v>-43.57923900000001</v>
+        <v>-44.2331124</v>
       </c>
       <c r="O87">
-        <v>-14.81694126</v>
+        <v>-15.039258216</v>
       </c>
       <c r="P87">
-        <v>-28.76229774</v>
+        <v>-29.193854184</v>
       </c>
       <c r="Q87">
-        <v>12.63770225999999</v>
+        <v>12.206145816</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.404557360466792</v>
+        <v>0.4301828862144199</v>
       </c>
       <c r="T87">
-        <v>4.675811069706291</v>
+        <v>5.009797574685312</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07340870572193332</v>
+        <v>0.0725551161205155</v>
       </c>
       <c r="W87">
-        <v>0.2184902271907681</v>
+        <v>0.2186915036187825</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2159079580056862</v>
+        <v>0.2133974003544573</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2483002971821717</v>
+        <v>0.2502002971821717</v>
       </c>
       <c r="C88">
-        <v>-68.06391432904064</v>
+        <v>-71.48140796964231</v>
       </c>
       <c r="D88">
-        <v>100.0140856709594</v>
+        <v>99.36959203035769</v>
       </c>
       <c r="E88">
-        <v>78.47800000000001</v>
+        <v>81.251</v>
       </c>
       <c r="F88">
-        <v>238.478</v>
+        <v>241.251</v>
       </c>
       <c r="G88">
         <v>70.40000000000001</v>
@@ -8491,37 +8491,37 @@
         <v>12</v>
       </c>
       <c r="M88">
-        <v>56.2331124</v>
+        <v>56.88698580000001</v>
       </c>
       <c r="N88">
-        <v>-44.2331124</v>
+        <v>-44.88698580000001</v>
       </c>
       <c r="O88">
-        <v>-15.039258216</v>
+        <v>-15.261575172</v>
       </c>
       <c r="P88">
-        <v>-29.193854184</v>
+        <v>-29.625410628</v>
       </c>
       <c r="Q88">
-        <v>12.206145816</v>
+        <v>11.77458937199999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4301828862144199</v>
+        <v>0.4597508005386061</v>
       </c>
       <c r="T88">
-        <v>5.009797574685312</v>
+        <v>5.395166618891874</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0725551161205155</v>
+        <v>0.07172114926855555</v>
       </c>
       <c r="W88">
-        <v>0.2186915036187825</v>
+        <v>0.2188881530024746</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2133974003544573</v>
+        <v>0.2109445566722222</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2502002971821717</v>
+        <v>0.2521002971821717</v>
       </c>
       <c r="C89">
-        <v>-71.48140796964231</v>
+        <v>-74.89064852231803</v>
       </c>
       <c r="D89">
-        <v>99.36959203035769</v>
+        <v>98.73335147768195</v>
       </c>
       <c r="E89">
-        <v>81.251</v>
+        <v>84.024</v>
       </c>
       <c r="F89">
-        <v>241.251</v>
+        <v>244.024</v>
       </c>
       <c r="G89">
         <v>70.40000000000001</v>
@@ -8573,37 +8573,37 @@
         <v>12</v>
       </c>
       <c r="M89">
-        <v>56.88698580000001</v>
+        <v>57.5408592</v>
       </c>
       <c r="N89">
-        <v>-44.88698580000001</v>
+        <v>-45.5408592</v>
       </c>
       <c r="O89">
-        <v>-15.261575172</v>
+        <v>-15.483892128</v>
       </c>
       <c r="P89">
-        <v>-29.625410628</v>
+        <v>-30.056967072</v>
       </c>
       <c r="Q89">
-        <v>11.77458937199999</v>
+        <v>11.343032928</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4597508005386061</v>
+        <v>0.49424670058349</v>
       </c>
       <c r="T89">
-        <v>5.395166618891874</v>
+        <v>5.844763837132865</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07172114926855555</v>
+        <v>0.07090613620868561</v>
       </c>
       <c r="W89">
-        <v>0.2188881530024746</v>
+        <v>0.219080333081992</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2109445566722222</v>
+        <v>0.2085474594373106</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2521002971821717</v>
+        <v>0.2540002971821717</v>
       </c>
       <c r="C90">
-        <v>-74.89064852231803</v>
+        <v>-78.29179350635724</v>
       </c>
       <c r="D90">
-        <v>98.73335147768195</v>
+        <v>98.1052064936428</v>
       </c>
       <c r="E90">
-        <v>84.024</v>
+        <v>86.79700000000003</v>
       </c>
       <c r="F90">
-        <v>244.024</v>
+        <v>246.797</v>
       </c>
       <c r="G90">
         <v>70.40000000000001</v>
@@ -8655,37 +8655,37 @@
         <v>12</v>
       </c>
       <c r="M90">
-        <v>57.5408592</v>
+        <v>58.19473260000001</v>
       </c>
       <c r="N90">
-        <v>-45.5408592</v>
+        <v>-46.19473260000001</v>
       </c>
       <c r="O90">
-        <v>-15.483892128</v>
+        <v>-15.706209084</v>
       </c>
       <c r="P90">
-        <v>-30.056967072</v>
+        <v>-30.488523516</v>
       </c>
       <c r="Q90">
-        <v>11.343032928</v>
+        <v>10.91147648399999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.49424670058349</v>
+        <v>0.5350145824547163</v>
       </c>
       <c r="T90">
-        <v>5.844763837132865</v>
+        <v>6.376106004144943</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07090613620868561</v>
+        <v>0.07010943804903744</v>
       </c>
       <c r="W90">
-        <v>0.219080333081992</v>
+        <v>0.219268194508037</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2085474594373106</v>
+        <v>0.2062042295559925</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2540002971821717</v>
+        <v>0.2559002971821717</v>
       </c>
       <c r="C91">
-        <v>-78.29179350635724</v>
+        <v>-81.6849964578179</v>
       </c>
       <c r="D91">
-        <v>98.1052064936428</v>
+        <v>97.48500354218213</v>
       </c>
       <c r="E91">
-        <v>86.79700000000003</v>
+        <v>89.57000000000002</v>
       </c>
       <c r="F91">
-        <v>246.797</v>
+        <v>249.57</v>
       </c>
       <c r="G91">
         <v>70.40000000000001</v>
@@ -8737,37 +8737,37 @@
         <v>12</v>
       </c>
       <c r="M91">
-        <v>58.19473260000001</v>
+        <v>58.84860600000001</v>
       </c>
       <c r="N91">
-        <v>-46.19473260000001</v>
+        <v>-46.84860600000001</v>
       </c>
       <c r="O91">
-        <v>-15.706209084</v>
+        <v>-15.92852604</v>
       </c>
       <c r="P91">
-        <v>-30.488523516</v>
+        <v>-30.92007996000001</v>
       </c>
       <c r="Q91">
-        <v>10.91147648399999</v>
+        <v>10.47992003999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5350145824547163</v>
+        <v>0.583936040700188</v>
       </c>
       <c r="T91">
-        <v>6.376106004144943</v>
+        <v>7.013716604559438</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07010943804903744</v>
+        <v>0.06933044429293703</v>
       </c>
       <c r="W91">
-        <v>0.219268194508037</v>
+        <v>0.2194518812357255</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2062042295559925</v>
+        <v>0.2039130714498147</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2559002971821717</v>
+        <v>0.2578002971821717</v>
       </c>
       <c r="C92">
-        <v>-81.6849964578179</v>
+        <v>-85.07040705464232</v>
       </c>
       <c r="D92">
-        <v>97.48500354218213</v>
+        <v>96.87259294535771</v>
       </c>
       <c r="E92">
-        <v>89.57000000000002</v>
+        <v>92.34300000000002</v>
       </c>
       <c r="F92">
-        <v>249.57</v>
+        <v>252.343</v>
       </c>
       <c r="G92">
         <v>70.40000000000001</v>
@@ -8819,37 +8819,37 @@
         <v>12</v>
       </c>
       <c r="M92">
-        <v>58.84860600000001</v>
+        <v>59.50247940000001</v>
       </c>
       <c r="N92">
-        <v>-46.84860600000001</v>
+        <v>-47.50247940000001</v>
       </c>
       <c r="O92">
-        <v>-15.92852604</v>
+        <v>-16.150842996</v>
       </c>
       <c r="P92">
-        <v>-30.92007996000001</v>
+        <v>-31.351636404</v>
       </c>
       <c r="Q92">
-        <v>10.47992003999999</v>
+        <v>10.04836359599999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.583936040700188</v>
+        <v>0.64372893411132</v>
       </c>
       <c r="T92">
-        <v>7.013716604559438</v>
+        <v>7.793018449510487</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06933044429293703</v>
+        <v>0.06856857127872894</v>
       </c>
       <c r="W92">
-        <v>0.2194518812357255</v>
+        <v>0.2196315308924757</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2039130714498147</v>
+        <v>0.2016722684668498</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2578002971821717</v>
+        <v>0.2597002971821717</v>
       </c>
       <c r="C93">
-        <v>-85.07040705464232</v>
+        <v>-88.4481712370858</v>
       </c>
       <c r="D93">
-        <v>96.87259294535771</v>
+        <v>96.26782876291419</v>
       </c>
       <c r="E93">
-        <v>92.34300000000002</v>
+        <v>95.11600000000001</v>
       </c>
       <c r="F93">
-        <v>252.343</v>
+        <v>255.116</v>
       </c>
       <c r="G93">
         <v>70.40000000000001</v>
@@ -8901,37 +8901,37 @@
         <v>12</v>
       </c>
       <c r="M93">
-        <v>59.50247940000001</v>
+        <v>60.15635280000001</v>
       </c>
       <c r="N93">
-        <v>-47.50247940000001</v>
+        <v>-48.15635280000001</v>
       </c>
       <c r="O93">
-        <v>-16.150842996</v>
+        <v>-16.37315995200001</v>
       </c>
       <c r="P93">
-        <v>-31.351636404</v>
+        <v>-31.783192848</v>
       </c>
       <c r="Q93">
-        <v>10.04836359599999</v>
+        <v>9.616807151999996</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.64372893411132</v>
+        <v>0.7184700508752352</v>
       </c>
       <c r="T93">
-        <v>7.793018449510487</v>
+        <v>8.7671457556993</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06856857127872894</v>
+        <v>0.06782326072135143</v>
       </c>
       <c r="W93">
-        <v>0.2196315308924757</v>
+        <v>0.2198072751219053</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2016722684668498</v>
+        <v>0.1994801785922101</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2597002971821717</v>
+        <v>0.2616002971821717</v>
       </c>
       <c r="C94">
-        <v>-88.4481712370858</v>
+        <v>-91.81843132366248</v>
       </c>
       <c r="D94">
-        <v>96.26782876291419</v>
+        <v>95.67056867633752</v>
       </c>
       <c r="E94">
-        <v>95.11600000000001</v>
+        <v>97.88900000000001</v>
       </c>
       <c r="F94">
-        <v>255.116</v>
+        <v>257.889</v>
       </c>
       <c r="G94">
         <v>70.40000000000001</v>
@@ -8983,37 +8983,37 @@
         <v>12</v>
       </c>
       <c r="M94">
-        <v>60.15635280000001</v>
+        <v>60.8102262</v>
       </c>
       <c r="N94">
-        <v>-48.15635280000001</v>
+        <v>-48.8102262</v>
       </c>
       <c r="O94">
-        <v>-16.37315995200001</v>
+        <v>-16.595476908</v>
       </c>
       <c r="P94">
-        <v>-31.783192848</v>
+        <v>-32.214749292</v>
       </c>
       <c r="Q94">
-        <v>9.616807151999996</v>
+        <v>9.185250707999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7184700508752352</v>
+        <v>0.8145657724288403</v>
       </c>
       <c r="T94">
-        <v>8.7671457556993</v>
+        <v>10.01959514937063</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06782326072135143</v>
+        <v>0.06709397834800358</v>
       </c>
       <c r="W94">
-        <v>0.2198072751219053</v>
+        <v>0.2199792399055408</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1994801785922101</v>
+        <v>0.1973352304353047</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2616002971821717</v>
+        <v>0.2635002971821717</v>
       </c>
       <c r="C95">
-        <v>-91.81843132366248</v>
+        <v>-95.18132612280164</v>
       </c>
       <c r="D95">
-        <v>95.67056867633752</v>
+        <v>95.08067387719838</v>
       </c>
       <c r="E95">
-        <v>97.88900000000001</v>
+        <v>100.662</v>
       </c>
       <c r="F95">
-        <v>257.889</v>
+        <v>260.662</v>
       </c>
       <c r="G95">
         <v>70.40000000000001</v>
@@ -9065,37 +9065,37 @@
         <v>12</v>
       </c>
       <c r="M95">
-        <v>60.8102262</v>
+        <v>61.46409960000001</v>
       </c>
       <c r="N95">
-        <v>-48.8102262</v>
+        <v>-49.46409960000001</v>
       </c>
       <c r="O95">
-        <v>-16.595476908</v>
+        <v>-16.81779386400001</v>
       </c>
       <c r="P95">
-        <v>-32.214749292</v>
+        <v>-32.646305736</v>
       </c>
       <c r="Q95">
-        <v>9.185250707999998</v>
+        <v>8.753694263999996</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8145657724288403</v>
+        <v>0.9426934011669805</v>
       </c>
       <c r="T95">
-        <v>10.01959514937063</v>
+        <v>11.68952767426574</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06709397834800358</v>
+        <v>0.06638021262089716</v>
       </c>
       <c r="W95">
-        <v>0.2199792399055408</v>
+        <v>0.2201475458639924</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1973352304353047</v>
+        <v>0.1952359194732269</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2635002971821717</v>
+        <v>0.2654002971821717</v>
       </c>
       <c r="C96">
-        <v>-95.18132612280164</v>
+        <v>-98.53699104039885</v>
       </c>
       <c r="D96">
-        <v>95.08067387719838</v>
+        <v>94.49800895960117</v>
       </c>
       <c r="E96">
-        <v>100.662</v>
+        <v>103.435</v>
       </c>
       <c r="F96">
-        <v>260.662</v>
+        <v>263.435</v>
       </c>
       <c r="G96">
         <v>70.40000000000001</v>
@@ -9147,37 +9147,37 @@
         <v>12</v>
       </c>
       <c r="M96">
-        <v>61.46409960000001</v>
+        <v>62.11797300000001</v>
       </c>
       <c r="N96">
-        <v>-49.46409960000001</v>
+        <v>-50.11797300000001</v>
       </c>
       <c r="O96">
-        <v>-16.81779386400001</v>
+        <v>-17.04011082</v>
       </c>
       <c r="P96">
-        <v>-32.646305736</v>
+        <v>-33.07786218</v>
       </c>
       <c r="Q96">
-        <v>8.753694263999996</v>
+        <v>8.322137819999995</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9426934011669805</v>
+        <v>1.122072081400377</v>
       </c>
       <c r="T96">
-        <v>11.68952767426574</v>
+        <v>14.02743320911889</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06638021262089716</v>
+        <v>0.06568147354067719</v>
       </c>
       <c r="W96">
-        <v>0.2201475458639924</v>
+        <v>0.2203123085391083</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1952359194732269</v>
+        <v>0.1931808045314035</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2654002971821717</v>
+        <v>0.2673002971821717</v>
       </c>
       <c r="C97">
-        <v>-98.53699104039885</v>
+        <v>-101.8855581834363</v>
       </c>
       <c r="D97">
-        <v>94.49800895960117</v>
+        <v>93.92244181656369</v>
       </c>
       <c r="E97">
-        <v>103.435</v>
+        <v>106.208</v>
       </c>
       <c r="F97">
-        <v>263.435</v>
+        <v>266.208</v>
       </c>
       <c r="G97">
         <v>70.40000000000001</v>
@@ -9229,37 +9229,37 @@
         <v>12</v>
       </c>
       <c r="M97">
-        <v>62.11797300000001</v>
+        <v>62.77184640000001</v>
       </c>
       <c r="N97">
-        <v>-50.11797300000001</v>
+        <v>-50.77184640000001</v>
       </c>
       <c r="O97">
-        <v>-17.04011082</v>
+        <v>-17.262427776</v>
       </c>
       <c r="P97">
-        <v>-33.07786218</v>
+        <v>-33.50941862400001</v>
       </c>
       <c r="Q97">
-        <v>8.322137819999995</v>
+        <v>7.890581375999993</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.122072081400377</v>
+        <v>1.391140101750472</v>
       </c>
       <c r="T97">
-        <v>14.02743320911889</v>
+        <v>17.53429151139862</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06568147354067719</v>
+        <v>0.06499729152462846</v>
       </c>
       <c r="W97">
-        <v>0.2203123085391083</v>
+        <v>0.2204736386584926</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1931808045314035</v>
+        <v>0.1911685044842013</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2673002971821717</v>
+        <v>0.2692002971821717</v>
       </c>
       <c r="C98">
-        <v>-101.8855581834363</v>
+        <v>-105.2271564598396</v>
       </c>
       <c r="D98">
-        <v>93.9224418165637</v>
+        <v>93.35384354016038</v>
       </c>
       <c r="E98">
-        <v>106.208</v>
+        <v>108.981</v>
       </c>
       <c r="F98">
-        <v>266.208</v>
+        <v>268.981</v>
       </c>
       <c r="G98">
         <v>70.40000000000001</v>
@@ -9311,37 +9311,37 @@
         <v>12</v>
       </c>
       <c r="M98">
-        <v>62.77184640000001</v>
+        <v>63.4257198</v>
       </c>
       <c r="N98">
-        <v>-50.77184640000001</v>
+        <v>-51.4257198</v>
       </c>
       <c r="O98">
-        <v>-17.262427776</v>
+        <v>-17.484744732</v>
       </c>
       <c r="P98">
-        <v>-33.50941862400001</v>
+        <v>-33.940975068</v>
       </c>
       <c r="Q98">
-        <v>7.890581375999993</v>
+        <v>7.459024931999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.391140101750469</v>
+        <v>1.839586802333959</v>
       </c>
       <c r="T98">
-        <v>17.53429151139858</v>
+        <v>23.37905534853144</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06499729152462846</v>
+        <v>0.06432721635427148</v>
       </c>
       <c r="W98">
-        <v>0.2204736386584926</v>
+        <v>0.2206316423836628</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1911685044842013</v>
+        <v>0.1891976951596219</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2692002971821717</v>
+        <v>0.2711002971821717</v>
       </c>
       <c r="C99">
-        <v>-105.2271564598396</v>
+        <v>-108.5619116747292</v>
       </c>
       <c r="D99">
-        <v>93.35384354016038</v>
+        <v>92.79208832527083</v>
       </c>
       <c r="E99">
-        <v>108.981</v>
+        <v>111.754</v>
       </c>
       <c r="F99">
-        <v>268.981</v>
+        <v>271.754</v>
       </c>
       <c r="G99">
         <v>70.40000000000001</v>
@@ -9393,37 +9393,37 @@
         <v>12</v>
       </c>
       <c r="M99">
-        <v>63.4257198</v>
+        <v>64.07959320000001</v>
       </c>
       <c r="N99">
-        <v>-51.4257198</v>
+        <v>-52.07959320000001</v>
       </c>
       <c r="O99">
-        <v>-17.484744732</v>
+        <v>-17.707061688</v>
       </c>
       <c r="P99">
-        <v>-33.940975068</v>
+        <v>-34.372531512</v>
       </c>
       <c r="Q99">
-        <v>7.459024931999998</v>
+        <v>7.027468487999997</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.839586802333959</v>
+        <v>2.736480203500937</v>
       </c>
       <c r="T99">
-        <v>23.37905534853144</v>
+        <v>35.06858302279716</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06432721635427148</v>
+        <v>0.06367081618739115</v>
       </c>
       <c r="W99">
-        <v>0.2206316423836628</v>
+        <v>0.2207864215430132</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1891976951596219</v>
+        <v>0.1872671064335034</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2711002971821717</v>
+        <v>0.2730002971821717</v>
       </c>
       <c r="C100">
-        <v>-108.5619116747292</v>
+        <v>-111.889946623217</v>
       </c>
       <c r="D100">
-        <v>92.79208832527083</v>
+        <v>92.237053376783</v>
       </c>
       <c r="E100">
-        <v>111.754</v>
+        <v>114.527</v>
       </c>
       <c r="F100">
-        <v>271.754</v>
+        <v>274.527</v>
       </c>
       <c r="G100">
         <v>70.40000000000001</v>
@@ -9475,37 +9475,37 @@
         <v>12</v>
       </c>
       <c r="M100">
-        <v>64.07959320000001</v>
+        <v>64.7334666</v>
       </c>
       <c r="N100">
-        <v>-52.07959320000001</v>
+        <v>-52.7334666</v>
       </c>
       <c r="O100">
-        <v>-17.707061688</v>
+        <v>-17.929378644</v>
       </c>
       <c r="P100">
-        <v>-34.372531512</v>
+        <v>-34.804087956</v>
       </c>
       <c r="Q100">
-        <v>7.027468487999997</v>
+        <v>6.595912043999995</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.736480203500937</v>
+        <v>5.427160407001875</v>
       </c>
       <c r="T100">
-        <v>35.06858302279716</v>
+        <v>70.13716604559431</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06367081618739115</v>
+        <v>0.06302767662994276</v>
       </c>
       <c r="W100">
-        <v>0.2207864215430132</v>
+        <v>0.2209380738506595</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1872671064335034</v>
+        <v>0.1853755194998317</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2730002971821717</v>
-      </c>
-      <c r="C101">
-        <v>-111.889946623217</v>
-      </c>
-      <c r="D101">
-        <v>92.237053376783</v>
-      </c>
-      <c r="E101">
-        <v>114.527</v>
-      </c>
-      <c r="F101">
-        <v>274.527</v>
-      </c>
-      <c r="G101">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="H101">
-        <v>117.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>53.4</v>
-      </c>
-      <c r="K101">
-        <v>41.4</v>
-      </c>
-      <c r="L101">
-        <v>12</v>
-      </c>
-      <c r="M101">
-        <v>64.7334666</v>
-      </c>
-      <c r="N101">
-        <v>-52.7334666</v>
-      </c>
-      <c r="O101">
-        <v>-17.929378644</v>
-      </c>
-      <c r="P101">
-        <v>-34.804087956</v>
-      </c>
-      <c r="Q101">
-        <v>6.595912043999995</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.427160407001875</v>
-      </c>
-      <c r="T101">
-        <v>70.13716604559431</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06302767662994276</v>
-      </c>
-      <c r="W101">
-        <v>0.2209380738506595</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1853755194998317</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
